--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_16oct26_Fri.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_16oct26_Fri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA70A125-7FE5-414E-B721-A62A9492FB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D296EA05-E6F5-49E3-A1E1-B1CB3D7837BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1499,17 +1499,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1917,7 +1917,7 @@
         <v>10880</v>
       </c>
       <c r="N2" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B2, $C$2:$C$649, C2, $D$2:$D$649, D2, $E$2:$E$649, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$649, B2, $C$2:$C$649, C2, $D$2:$D$649, D2, $E$2:$E$649, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -1965,7 +1965,7 @@
         <v>10680</v>
       </c>
       <c r="N3" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B3, $C$2:$C$649, C3, $D$2:$D$649, D3, $E$2:$E$649, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -2006,7 +2006,7 @@
       <c r="L4" s="16"/>
       <c r="M4" s="16"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B4, $C$2:$C$649, C4, $D$2:$D$649, D4, $E$2:$E$649, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       <c r="L5" s="16"/>
       <c r="M5" s="16"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B5, $C$2:$C$649, C5, $D$2:$D$649, D5, $E$2:$E$649, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
         <v>3156</v>
       </c>
       <c r="N6" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B6, $C$2:$C$649, C6, $D$2:$D$649, D6, $E$2:$E$649, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -2126,7 +2126,7 @@
       <c r="L7" s="16"/>
       <c r="M7" s="16"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B7, $C$2:$C$649, C7, $D$2:$D$649, D7, $E$2:$E$649, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B8, $C$2:$C$649, C8, $D$2:$D$649, D8, $E$2:$E$649, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
         <v>450</v>
       </c>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B9, $C$2:$C$649, C9, $D$2:$D$649, D9, $E$2:$E$649, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
@@ -2257,7 +2257,7 @@
         <v>700</v>
       </c>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B10, $C$2:$C$649, C10, $D$2:$D$649, D10, $E$2:$E$649, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="10"/>
@@ -2305,7 +2305,7 @@
         <v>264</v>
       </c>
       <c r="N11" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B11, $C$2:$C$649, C11, $D$2:$D$649, D11, $E$2:$E$649, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="10"/>
@@ -2353,7 +2353,7 @@
         <v>240</v>
       </c>
       <c r="N12" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B12, $C$2:$C$649, C12, $D$2:$D$649, D12, $E$2:$E$649, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
@@ -2394,7 +2394,7 @@
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B13, $C$2:$C$649, C13, $D$2:$D$649, D13, $E$2:$E$649, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13"/>
@@ -2435,7 +2435,7 @@
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B14, $C$2:$C$649, C14, $D$2:$D$649, D14, $E$2:$E$649, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14"/>
@@ -2483,7 +2483,7 @@
         <v>800</v>
       </c>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B15, $C$2:$C$649, C15, $D$2:$D$649, D15, $E$2:$E$649, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
         <v>1300</v>
       </c>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B16, $C$2:$C$649, C16, $D$2:$D$649, D16, $E$2:$E$649, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B17, $C$2:$C$649, C17, $D$2:$D$649, D17, $E$2:$E$649, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17"/>
@@ -2616,7 +2616,7 @@
         <v>360</v>
       </c>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B18, $C$2:$C$649, C18, $D$2:$D$649, D18, $E$2:$E$649, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="10"/>
@@ -2655,7 +2655,7 @@
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B19, $C$2:$C$649, C19, $D$2:$D$649, D19, $E$2:$E$649, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19"/>
@@ -2694,7 +2694,7 @@
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B20, $C$2:$C$649, C20, $D$2:$D$649, D20, $E$2:$E$649, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20"/>
@@ -2742,7 +2742,7 @@
         <v>295</v>
       </c>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B21, $C$2:$C$649, C21, $D$2:$D$649, D21, $E$2:$E$649, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B22, $C$2:$C$649, C22, $D$2:$D$649, D22, $E$2:$E$649, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22"/>
@@ -2827,7 +2827,7 @@
         <v>250</v>
       </c>
       <c r="N23" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B23, $C$2:$C$649, C23, $D$2:$D$649, D23, $E$2:$E$649, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B24, $C$2:$C$649, C24, $D$2:$D$649, D24, $E$2:$E$649, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -2912,7 +2912,7 @@
         <v>660</v>
       </c>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B25, $C$2:$C$649, C25, $D$2:$D$649, D25, $E$2:$E$649, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
         <v>225</v>
       </c>
       <c r="N26" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B26, $C$2:$C$649, C26, $D$2:$D$649, D26, $E$2:$E$649, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
         <v>540</v>
       </c>
       <c r="N27" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B27, $C$2:$C$649, C27, $D$2:$D$649, D27, $E$2:$E$649, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27"/>
@@ -3047,7 +3047,7 @@
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B28, $C$2:$C$649, C28, $D$2:$D$649, D28, $E$2:$E$649, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
@@ -3086,7 +3086,7 @@
       <c r="L29" s="16"/>
       <c r="M29" s="16"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B29, $C$2:$C$649, C29, $D$2:$D$649, D29, $E$2:$E$649, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29"/>
@@ -3125,7 +3125,7 @@
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B30, $C$2:$C$649, C30, $D$2:$D$649, D30, $E$2:$E$649, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30"/>
@@ -3166,7 +3166,7 @@
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B31, $C$2:$C$649, C31, $D$2:$D$649, D31, $E$2:$E$649, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -3214,7 +3214,7 @@
         <v>250</v>
       </c>
       <c r="N32" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B32, $C$2:$C$649, C32, $D$2:$D$649, D32, $E$2:$E$649, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32" s="10"/>
@@ -3263,7 +3263,7 @@
         <v>220</v>
       </c>
       <c r="N33" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B33, $C$2:$C$649, C33, $D$2:$D$649, D33, $E$2:$E$649, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       <c r="L34" s="16"/>
       <c r="M34" s="16"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B34, $C$2:$C$649, C34, $D$2:$D$649, D34, $E$2:$E$649, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -3349,7 +3349,7 @@
         <v>448</v>
       </c>
       <c r="N35" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B35, $C$2:$C$649, C35, $D$2:$D$649, D35, $E$2:$E$649, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35" s="10"/>
@@ -3397,7 +3397,7 @@
         <v>250</v>
       </c>
       <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B36, $C$2:$C$649, C36, $D$2:$D$649, D36, $E$2:$E$649, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B37, $C$2:$C$649, C37, $D$2:$D$649, D37, $E$2:$E$649, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -3482,7 +3482,7 @@
         <v>300</v>
       </c>
       <c r="N38" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B38, $C$2:$C$649, C38, $D$2:$D$649, D38, $E$2:$E$649, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38" s="10"/>
@@ -3531,7 +3531,7 @@
         <v>440</v>
       </c>
       <c r="N39" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B39, $C$2:$C$649, C39, $D$2:$D$649, D39, $E$2:$E$649, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39" s="10"/>
@@ -3580,7 +3580,7 @@
         <v>235</v>
       </c>
       <c r="N40" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B40, $C$2:$C$649, C40, $D$2:$D$649, D40, $E$2:$E$649, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40" s="10"/>
@@ -3614,12 +3614,12 @@
       <c r="I41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="80"/>
+      <c r="J41" s="43"/>
       <c r="K41" s="16"/>
       <c r="L41" s="16"/>
       <c r="M41" s="16"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B41, $C$2:$C$649, C41, $D$2:$D$649, D41, $E$2:$E$649, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -3667,7 +3667,7 @@
         <v>253</v>
       </c>
       <c r="N42" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B42, $C$2:$C$649, C42, $D$2:$D$649, D42, $E$2:$E$649, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42" s="10"/>
@@ -3716,7 +3716,7 @@
         <v>240</v>
       </c>
       <c r="N43" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B43, $C$2:$C$649, C43, $D$2:$D$649, D43, $E$2:$E$649, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43" s="10"/>
@@ -3750,7 +3750,7 @@
       <c r="I44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="77" t="s">
+      <c r="J44" s="17" t="s">
         <v>40</v>
       </c>
       <c r="K44" t="s">
@@ -3764,7 +3764,7 @@
         <v>250</v>
       </c>
       <c r="N44" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B44, $C$2:$C$649, C44, $D$2:$D$649, D44, $E$2:$E$649, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44" s="10"/>
@@ -3803,7 +3803,7 @@
       <c r="L45" s="16"/>
       <c r="M45" s="16"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B45, $C$2:$C$649, C45, $D$2:$D$649, D45, $E$2:$E$649, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -3851,7 +3851,7 @@
         <v>50</v>
       </c>
       <c r="N46" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B46, $C$2:$C$649, C46, $D$2:$D$649, D46, $E$2:$E$649, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O46" s="27"/>
@@ -3899,7 +3899,7 @@
         <v>150</v>
       </c>
       <c r="N47" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B47, $C$2:$C$649, C47, $D$2:$D$649, D47, $E$2:$E$649, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O47" s="27"/>
@@ -3947,7 +3947,7 @@
         <v>350</v>
       </c>
       <c r="N48" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B48, $C$2:$C$649, C48, $D$2:$D$649, D48, $E$2:$E$649, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O48" s="27"/>
@@ -3995,7 +3995,7 @@
         <v>250</v>
       </c>
       <c r="N49" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B49, $C$2:$C$649, C49, $D$2:$D$649, D49, $E$2:$E$649, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
         <v>689.99999999999636</v>
       </c>
       <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B50, $C$2:$C$649, C50, $D$2:$D$649, D50, $E$2:$E$649, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50" s="10"/>
@@ -4080,7 +4080,7 @@
       <c r="L51" s="16"/>
       <c r="M51" s="16"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B51, $C$2:$C$649, C51, $D$2:$D$649, D51, $E$2:$E$649, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -4128,7 +4128,7 @@
         <v>400</v>
       </c>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B52, $C$2:$C$649, C52, $D$2:$D$649, D52, $E$2:$E$649, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="10"/>
@@ -4169,7 +4169,7 @@
       <c r="L53" s="16"/>
       <c r="M53" s="16"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B53, $C$2:$C$649, C53, $D$2:$D$649, D53, $E$2:$E$649, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
@@ -4218,7 +4218,7 @@
         <v>135</v>
       </c>
       <c r="N54" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B54, $C$2:$C$649, C54, $D$2:$D$649, D54, $E$2:$E$649, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       <c r="L55" s="61"/>
       <c r="M55" s="61"/>
       <c r="N55" s="53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B55, $C$2:$C$649, C55, $D$2:$D$649, D55, $E$2:$E$649, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55" s="53"/>
@@ -4305,7 +4305,7 @@
         <v>700</v>
       </c>
       <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B56, $C$2:$C$649, C56, $D$2:$D$649, D56, $E$2:$E$649, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
         <v>470</v>
       </c>
       <c r="N57" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B57, $C$2:$C$649, C57, $D$2:$D$649, D57, $E$2:$E$649, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
         <v>300</v>
       </c>
       <c r="N58" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B58, $C$2:$C$649, C58, $D$2:$D$649, D58, $E$2:$E$649, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         <v>660</v>
       </c>
       <c r="N59" s="64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B59, $C$2:$C$649, C59, $D$2:$D$649, D59, $E$2:$E$649, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59" s="64"/>
@@ -4491,7 +4491,7 @@
         <v>650</v>
       </c>
       <c r="N60" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B60, $C$2:$C$649, C60, $D$2:$D$649, D60, $E$2:$E$649, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60" s="10"/>
@@ -4525,14 +4525,14 @@
       <c r="I61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J61" s="79" t="s">
+      <c r="J61" s="44" t="s">
         <v>40</v>
       </c>
       <c r="K61" s="16"/>
       <c r="L61" s="16"/>
       <c r="M61" s="16"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B61, $C$2:$C$649, C61, $D$2:$D$649, D61, $E$2:$E$649, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61"/>
@@ -4573,7 +4573,7 @@
       <c r="L62" s="16"/>
       <c r="M62" s="16"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B62, $C$2:$C$649, C62, $D$2:$D$649, D62, $E$2:$E$649, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4615,11 +4615,11 @@
         <v>35560</v>
       </c>
       <c r="M63" s="17">
-        <f>ABS((D63*E63)-L63)</f>
+        <f t="shared" ref="M63:M68" si="1">ABS((D63*E63)-L63)</f>
         <v>720</v>
       </c>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B63, $C$2:$C$649, C63, $D$2:$D$649, D63, $E$2:$E$649, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4661,11 +4661,11 @@
         <v>18855</v>
       </c>
       <c r="M64" s="17">
-        <f>ABS((D64*E64)-L64)</f>
+        <f t="shared" si="1"/>
         <v>360</v>
       </c>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B64, $C$2:$C$649, C64, $D$2:$D$649, D64, $E$2:$E$649, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4707,11 +4707,11 @@
         <v>8970</v>
       </c>
       <c r="M65" s="17">
-        <f>ABS((D65*E65)-L65)</f>
+        <f t="shared" si="1"/>
         <v>250</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B65, $C$2:$C$649, C65, $D$2:$D$649, D65, $E$2:$E$649, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4753,11 +4753,11 @@
         <v>14860</v>
       </c>
       <c r="M66" s="17">
-        <f>ABS((D66*E66)-L66)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B66, $C$2:$C$649, C66, $D$2:$D$649, D66, $E$2:$E$649, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="2">IF(COUNTIFS( $B$2:$B$649, B66, $C$2:$C$649, C66, $D$2:$D$649, D66, $E$2:$E$649, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -4799,11 +4799,11 @@
         <v>33800</v>
       </c>
       <c r="M67" s="17">
-        <f>ABS((D67*E67)-L67)</f>
+        <f t="shared" si="1"/>
         <v>700</v>
       </c>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B67, $C$2:$C$649, C67, $D$2:$D$649, D67, $E$2:$E$649, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4845,11 +4845,11 @@
         <v>14450</v>
       </c>
       <c r="M68" s="17">
-        <f>ABS((D68*E68)-L68)</f>
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
       <c r="N68" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B68, $C$2:$C$649, C68, $D$2:$D$649, D68, $E$2:$E$649, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       <c r="L69" s="16"/>
       <c r="M69" s="16"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B69, $C$2:$C$649, C69, $D$2:$D$649, D69, $E$2:$E$649, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
@@ -4927,7 +4927,7 @@
       <c r="L70" s="16"/>
       <c r="M70" s="16"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B70, $C$2:$C$649, C70, $D$2:$D$649, D70, $E$2:$E$649, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
@@ -4965,7 +4965,7 @@
       <c r="L71" s="16"/>
       <c r="M71" s="16"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B71, $C$2:$C$649, C71, $D$2:$D$649, D71, $E$2:$E$649, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O71"/>
@@ -5008,7 +5008,7 @@
       <c r="L72" s="16"/>
       <c r="M72" s="16"/>
       <c r="N72" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B72, $C$2:$C$649, C72, $D$2:$D$649, D72, $E$2:$E$649, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O72"/>
@@ -5049,7 +5049,7 @@
       <c r="L73" s="16"/>
       <c r="M73" s="16"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B73, $C$2:$C$649, C73, $D$2:$D$649, D73, $E$2:$E$649, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P73"/>
@@ -5096,7 +5096,7 @@
         <v>500</v>
       </c>
       <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B74, $C$2:$C$649, C74, $D$2:$D$649, D74, $E$2:$E$649, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       <c r="L75" s="16"/>
       <c r="M75" s="16"/>
       <c r="N75" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B75, $C$2:$C$649, C75, $D$2:$D$649, D75, $E$2:$E$649, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O75"/>
@@ -5176,7 +5176,7 @@
       <c r="L76" s="16"/>
       <c r="M76" s="16"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B76, $C$2:$C$649, C76, $D$2:$D$649, D76, $E$2:$E$649, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>1200</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B77, $C$2:$C$649, C77, $D$2:$D$649, D77, $E$2:$E$649, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O77" s="36" t="s">
@@ -5272,7 +5272,7 @@
         <v>200</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B78, $C$2:$C$649, C78, $D$2:$D$649, D78, $E$2:$E$649, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
         <v>117</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B79, $C$2:$C$649, C79, $D$2:$D$649, D79, $E$2:$E$649, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
         <v>250</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B80, $C$2:$C$649, C80, $D$2:$D$649, D80, $E$2:$E$649, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="36" t="s">
@@ -5403,7 +5403,7 @@
         <v>300</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B81, $C$2:$C$649, C81, $D$2:$D$649, D81, $E$2:$E$649, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P81" s="22"/>
@@ -5450,7 +5450,7 @@
         <v>516</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B82, $C$2:$C$649, C82, $D$2:$D$649, D82, $E$2:$E$649, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       <c r="L83" s="16"/>
       <c r="M83" s="16"/>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B83, $C$2:$C$649, C83, $D$2:$D$649, D83, $E$2:$E$649, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O83"/>
@@ -5537,7 +5537,7 @@
         <v>300</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B84, $C$2:$C$649, C84, $D$2:$D$649, D84, $E$2:$E$649, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O84" s="36" t="s">
@@ -5586,7 +5586,7 @@
         <v>11409.000000000004</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B85, $C$2:$C$649, C85, $D$2:$D$649, D85, $E$2:$E$649, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P85"/>
@@ -5634,7 +5634,7 @@
         <v>300</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B86, $C$2:$C$649, C86, $D$2:$D$649, D86, $E$2:$E$649, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O86" s="36" t="s">
@@ -5673,7 +5673,7 @@
         <v>117</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B87, $C$2:$C$649, C87, $D$2:$D$649, D87, $E$2:$E$649, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P87"/>
@@ -5716,11 +5716,11 @@
         <v>32900</v>
       </c>
       <c r="M88" s="17">
-        <f>ABS((D88*E88)-L88)</f>
+        <f t="shared" ref="M88:M97" si="3">ABS((D88*E88)-L88)</f>
         <v>1000</v>
       </c>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B88, $C$2:$C$649, C88, $D$2:$D$649, D88, $E$2:$E$649, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="10"/>
@@ -5764,11 +5764,11 @@
         <v>16755</v>
       </c>
       <c r="M89" s="17">
-        <f>ABS((D89*E89)-L89)</f>
+        <f t="shared" si="3"/>
         <v>295</v>
       </c>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B89, $C$2:$C$649, C89, $D$2:$D$649, D89, $E$2:$E$649, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5810,11 +5810,11 @@
         <v>8570</v>
       </c>
       <c r="M90" s="25">
-        <f>ABS((D90*E90)-L90)</f>
+        <f t="shared" si="3"/>
         <v>650</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B90, $C$2:$C$649, C90, $D$2:$D$649, D90, $E$2:$E$649, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="36" t="s">
@@ -5859,11 +5859,11 @@
         <v>17020</v>
       </c>
       <c r="M91" s="17">
-        <f>ABS((D91*E91)-L91)</f>
+        <f t="shared" si="3"/>
         <v>650</v>
       </c>
       <c r="N91" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B91, $C$2:$C$649, C91, $D$2:$D$649, D91, $E$2:$E$649, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5906,11 +5906,11 @@
         <v>8970</v>
       </c>
       <c r="M92" s="17">
-        <f>ABS((D92*E92)-L92)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B92, $C$2:$C$649, C92, $D$2:$D$649, D92, $E$2:$E$649, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5952,11 +5952,11 @@
         <v>5620</v>
       </c>
       <c r="M93" s="25">
-        <f>ABS((D93*E93)-L93)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B93, $C$2:$C$649, C93, $D$2:$D$649, D93, $E$2:$E$649, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O93" s="10"/>
@@ -6000,11 +6000,11 @@
         <v>6127.5</v>
       </c>
       <c r="M94" s="25">
-        <f>ABS((D94*E94)-L94)</f>
+        <f t="shared" si="3"/>
         <v>612.5</v>
       </c>
       <c r="N94" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B94, $C$2:$C$649, C94, $D$2:$D$649, D94, $E$2:$E$649, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O94" s="27"/>
@@ -6048,11 +6048,11 @@
         <v>6320</v>
       </c>
       <c r="M95" s="25">
-        <f>ABS((D95*E95)-L95)</f>
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
       <c r="N95" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B95, $C$2:$C$649, C95, $D$2:$D$649, D95, $E$2:$E$649, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O95" s="27"/>
@@ -6096,11 +6096,11 @@
         <v>8220</v>
       </c>
       <c r="M96" s="17">
-        <f>ABS((D96*E96)-L96)</f>
+        <f t="shared" si="3"/>
         <v>360</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B96, $C$2:$C$649, C96, $D$2:$D$649, D96, $E$2:$E$649, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O96" s="36" t="s">
@@ -6145,11 +6145,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M97" s="17">
-        <f>ABS((D97*E97)-L97)</f>
+        <f t="shared" si="3"/>
         <v>14149.000000000004</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B97, $C$2:$C$649, C97, $D$2:$D$649, D97, $E$2:$E$649, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O97" s="10"/>
@@ -6188,7 +6188,7 @@
       <c r="L98" s="16"/>
       <c r="M98" s="16"/>
       <c r="N98" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B98, $C$2:$C$649, C98, $D$2:$D$649, D98, $E$2:$E$649, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6234,50 +6234,48 @@
         <v>1200</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B99, $C$2:$C$649, C99, $D$2:$D$649, D99, $E$2:$E$649, E99) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" s="27" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="8" t="s">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" s="23" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C100" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D100" s="8">
+      <c r="C100" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="12">
         <v>11</v>
       </c>
       <c r="E100" s="12">
         <v>749</v>
       </c>
-      <c r="F100" s="4">
+      <c r="F100" s="52">
         <v>5.0933071419999996</v>
       </c>
-      <c r="G100" s="2" t="s">
+      <c r="G100" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="H100" s="5">
+      <c r="H100" s="78">
         <v>712.7</v>
       </c>
-      <c r="I100" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="32" t="s">
+      <c r="I100" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="79" t="s">
         <v>190</v>
       </c>
-      <c r="K100" s="17"/>
-      <c r="L100" s="17"/>
-      <c r="M100" s="17"/>
-      <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B100, $C$2:$C$649, C100, $D$2:$D$649, D100, $E$2:$E$649, E100) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O100" s="10"/>
-      <c r="P100" s="10"/>
+      <c r="K100" s="80"/>
+      <c r="L100" s="80"/>
+      <c r="M100" s="80"/>
+      <c r="N100" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="101" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3">
@@ -6321,7 +6319,7 @@
         <v>300</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B101, $C$2:$C$649, C101, $D$2:$D$649, D101, $E$2:$E$649, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6367,7 +6365,7 @@
         <v>660</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B102, $C$2:$C$649, C102, $D$2:$D$649, D102, $E$2:$E$649, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6404,7 +6402,7 @@
       <c r="L103" s="16"/>
       <c r="M103" s="16"/>
       <c r="N103" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B103, $C$2:$C$649, C103, $D$2:$D$649, D103, $E$2:$E$649, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6450,7 +6448,7 @@
         <v>200</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B104, $C$2:$C$649, C104, $D$2:$D$649, D104, $E$2:$E$649, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="10"/>
@@ -6491,7 +6489,7 @@
       <c r="L105" s="16"/>
       <c r="M105" s="16"/>
       <c r="N105" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B105, $C$2:$C$649, C105, $D$2:$D$649, D105, $E$2:$E$649, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="10"/>
@@ -6539,7 +6537,7 @@
         <v>250</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B106, $C$2:$C$649, C106, $D$2:$D$649, D106, $E$2:$E$649, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O106" s="10"/>
@@ -6587,7 +6585,7 @@
         <v>650</v>
       </c>
       <c r="N107" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B107, $C$2:$C$649, C107, $D$2:$D$649, D107, $E$2:$E$649, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6633,7 +6631,7 @@
         <v>850</v>
       </c>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B108, $C$2:$C$649, C108, $D$2:$D$649, D108, $E$2:$E$649, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6665,12 +6663,12 @@
       <c r="I109" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J109" s="80"/>
+      <c r="J109" s="43"/>
       <c r="K109" s="16"/>
       <c r="L109" s="16"/>
       <c r="M109" s="16"/>
       <c r="N109" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B109, $C$2:$C$649, C109, $D$2:$D$649, D109, $E$2:$E$649, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="18"/>
@@ -6710,7 +6708,7 @@
       <c r="L110" s="16"/>
       <c r="M110" s="16"/>
       <c r="N110" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B110, $C$2:$C$649, C110, $D$2:$D$649, D110, $E$2:$E$649, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6756,7 +6754,7 @@
         <v>300</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B111, $C$2:$C$649, C111, $D$2:$D$649, D111, $E$2:$E$649, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6802,7 +6800,7 @@
         <v>300</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B112, $C$2:$C$649, C112, $D$2:$D$649, D112, $E$2:$E$649, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6848,7 +6846,7 @@
         <v>300</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B113, $C$2:$C$649, C113, $D$2:$D$649, D113, $E$2:$E$649, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6894,7 +6892,7 @@
         <v>274</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B114, $C$2:$C$649, C114, $D$2:$D$649, D114, $E$2:$E$649, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6930,7 +6928,7 @@
         <v>117</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B115, $C$2:$C$649, C115, $D$2:$D$649, D115, $E$2:$E$649, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6976,7 +6974,7 @@
         <v>390</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B116, $C$2:$C$649, C116, $D$2:$D$649, D116, $E$2:$E$649, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="10"/>
@@ -7024,7 +7022,7 @@
         <v>500</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B117, $C$2:$C$649, C117, $D$2:$D$649, D117, $E$2:$E$649, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="10"/>
@@ -7072,7 +7070,7 @@
         <v>650</v>
       </c>
       <c r="N118" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B118, $C$2:$C$649, C118, $D$2:$D$649, D118, $E$2:$E$649, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="27"/>
@@ -7120,7 +7118,7 @@
         <v>934</v>
       </c>
       <c r="N119" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B119, $C$2:$C$649, C119, $D$2:$D$649, D119, $E$2:$E$649, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="27"/>
@@ -7168,7 +7166,7 @@
         <v>654.5</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B120, $C$2:$C$649, C120, $D$2:$D$649, D120, $E$2:$E$649, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="36" t="s">
@@ -7208,7 +7206,7 @@
       <c r="L121" s="16"/>
       <c r="M121" s="16"/>
       <c r="N121" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B121, $C$2:$C$649, C121, $D$2:$D$649, D121, $E$2:$E$649, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="23"/>
@@ -7241,14 +7239,14 @@
       <c r="I122" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J122" s="78" t="s">
+      <c r="J122" s="49" t="s">
         <v>40</v>
       </c>
       <c r="K122" s="16"/>
       <c r="L122" s="16"/>
       <c r="M122" s="16"/>
       <c r="N122" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B122, $C$2:$C$649, C122, $D$2:$D$649, D122, $E$2:$E$649, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="37" t="s">
@@ -7298,7 +7296,7 @@
         <v>656.5</v>
       </c>
       <c r="N123" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B123, $C$2:$C$649, C123, $D$2:$D$649, D123, $E$2:$E$649, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7344,7 +7342,7 @@
         <v>265</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B124, $C$2:$C$649, C124, $D$2:$D$649, D124, $E$2:$E$649, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7390,7 +7388,7 @@
         <v>654</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B125, $C$2:$C$649, C125, $D$2:$D$649, D125, $E$2:$E$649, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O125" s="36" t="s">
@@ -7432,7 +7430,7 @@
         <v>143</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B126, $C$2:$C$649, C126, $D$2:$D$649, D126, $E$2:$E$649, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7478,7 +7476,7 @@
         <v>300</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B127, $C$2:$C$649, C127, $D$2:$D$649, D127, $E$2:$E$649, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P127" s="18"/>
@@ -7516,7 +7514,7 @@
       <c r="L128" s="17"/>
       <c r="M128" s="17"/>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B128, $C$2:$C$649, C128, $D$2:$D$649, D128, $E$2:$E$649, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="10"/>
@@ -7560,11 +7558,11 @@
         <v>5820</v>
       </c>
       <c r="M129" s="17">
-        <f>ABS((D129*E129)-L129)</f>
+        <f t="shared" ref="M129:M136" si="4">ABS((D129*E129)-L129)</f>
         <v>300</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B129, $C$2:$C$649, C129, $D$2:$D$649, D129, $E$2:$E$649, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7606,11 +7604,11 @@
         <v>39300</v>
       </c>
       <c r="M130" s="17">
-        <f>ABS((D130*E130)-L130)</f>
+        <f t="shared" si="4"/>
         <v>18850</v>
       </c>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B130, $C$2:$C$649, C130, $D$2:$D$649, D130, $E$2:$E$649, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="5">IF(COUNTIFS( $B$2:$B$649, B130, $C$2:$C$649, C130, $D$2:$D$649, D130, $E$2:$E$649, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7652,11 +7650,11 @@
         <v>16500</v>
       </c>
       <c r="M131" s="17">
-        <f>ABS((D131*E131)-L131)</f>
+        <f t="shared" si="4"/>
         <v>1400</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B131, $C$2:$C$649, C131, $D$2:$D$649, D131, $E$2:$E$649, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="36" t="s">
@@ -7701,11 +7699,11 @@
         <v>37480</v>
       </c>
       <c r="M132" s="17">
-        <f>ABS((D132*E132)-L132)</f>
+        <f t="shared" si="4"/>
         <v>1000</v>
       </c>
       <c r="N132" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B132, $C$2:$C$649, C132, $D$2:$D$649, D132, $E$2:$E$649, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P132" s="27"/>
@@ -7748,11 +7746,11 @@
         <v>10550</v>
       </c>
       <c r="M133" s="17">
-        <f>ABS((D133*E133)-L133)</f>
+        <f t="shared" si="4"/>
         <v>350</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B133, $C$2:$C$649, C133, $D$2:$D$649, D133, $E$2:$E$649, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="10"/>
@@ -7796,11 +7794,11 @@
         <v>15075</v>
       </c>
       <c r="M134" s="17">
-        <f>ABS((D134*E134)-L134)</f>
+        <f t="shared" si="4"/>
         <v>645</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B134, $C$2:$C$649, C134, $D$2:$D$649, D134, $E$2:$E$649, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="36" t="s">
@@ -7845,11 +7843,11 @@
         <v>3024.2</v>
       </c>
       <c r="M135" s="17">
-        <f>ABS((D135*E135)-L135)</f>
+        <f t="shared" si="4"/>
         <v>271.80000000000018</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B135, $C$2:$C$649, C135, $D$2:$D$649, D135, $E$2:$E$649, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7891,11 +7889,11 @@
         <v>12800</v>
       </c>
       <c r="M136" s="17">
-        <f>ABS((D136*E136)-L136)</f>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B136, $C$2:$C$649, C136, $D$2:$D$649, D136, $E$2:$E$649, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7929,7 +7927,7 @@
       </c>
       <c r="J137" s="32"/>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B137, $C$2:$C$649, C137, $D$2:$D$649, D137, $E$2:$E$649, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="27"/>
@@ -7966,7 +7964,7 @@
         <v>116</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B138, $C$2:$C$649, C138, $D$2:$D$649, D138, $E$2:$E$649, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8008,11 +8006,11 @@
         <v>34100</v>
       </c>
       <c r="M139" s="17">
-        <f>ABS((D139*E139)-L139)</f>
+        <f t="shared" ref="M139:M150" si="6">ABS((D139*E139)-L139)</f>
         <v>1700</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B139, $C$2:$C$649, C139, $D$2:$D$649, D139, $E$2:$E$649, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="27"/>
@@ -8055,11 +8053,11 @@
         <v>7578</v>
       </c>
       <c r="M140" s="25">
-        <f>ABS((D140*E140)-L140)</f>
+        <f t="shared" si="6"/>
         <v>294</v>
       </c>
       <c r="N140" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B140, $C$2:$C$649, C140, $D$2:$D$649, D140, $E$2:$E$649, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8101,11 +8099,11 @@
         <v>7578</v>
       </c>
       <c r="M141" s="25">
-        <f>ABS((D141*E141)-L141)</f>
+        <f t="shared" si="6"/>
         <v>294</v>
       </c>
       <c r="N141" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B141, $C$2:$C$649, C141, $D$2:$D$649, D141, $E$2:$E$649, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8147,11 +8145,11 @@
         <v>4968</v>
       </c>
       <c r="M142" s="25">
-        <f>ABS((D142*E142)-L142)</f>
+        <f t="shared" si="6"/>
         <v>280</v>
       </c>
       <c r="N142" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B142, $C$2:$C$649, C142, $D$2:$D$649, D142, $E$2:$E$649, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O142" s="27"/>
@@ -8195,11 +8193,11 @@
         <v>17040</v>
       </c>
       <c r="M143" s="17">
-        <f>ABS((D143*E143)-L143)</f>
+        <f t="shared" si="6"/>
         <v>880</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B143, $C$2:$C$649, C143, $D$2:$D$649, D143, $E$2:$E$649, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="36" t="s">
@@ -8245,11 +8243,11 @@
         <v>6900</v>
       </c>
       <c r="M144" s="17">
-        <f>ABS((D144*E144)-L144)</f>
+        <f t="shared" si="6"/>
         <v>444</v>
       </c>
       <c r="N144" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B144, $C$2:$C$649, C144, $D$2:$D$649, D144, $E$2:$E$649, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8291,11 +8289,11 @@
         <v>4120</v>
       </c>
       <c r="M145" s="25">
-        <f>ABS((D145*E145)-L145)</f>
+        <f t="shared" si="6"/>
         <v>270</v>
       </c>
       <c r="N145" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B145, $C$2:$C$649, C145, $D$2:$D$649, D145, $E$2:$E$649, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O145" s="37" t="s">
@@ -8341,11 +8339,11 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M146" s="25">
-        <f>ABS((D146*E146)-L146)</f>
+        <f t="shared" si="6"/>
         <v>188.60000000000014</v>
       </c>
       <c r="N146" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B146, $C$2:$C$649, C146, $D$2:$D$649, D146, $E$2:$E$649, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="37" t="s">
@@ -8391,11 +8389,11 @@
         <v>38020</v>
       </c>
       <c r="M147" s="17">
-        <f>ABS((D147*E147)-L147)</f>
+        <f t="shared" si="6"/>
         <v>940</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B147, $C$2:$C$649, C147, $D$2:$D$649, D147, $E$2:$E$649, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8437,11 +8435,11 @@
         <v>10300</v>
       </c>
       <c r="M148" s="17">
-        <f>ABS((D148*E148)-L148)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B148, $C$2:$C$649, C148, $D$2:$D$649, D148, $E$2:$E$649, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P148" s="27"/>
@@ -8484,11 +8482,11 @@
         <v>11360</v>
       </c>
       <c r="M149" s="17">
-        <f>ABS((D149*E149)-L149)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B149, $C$2:$C$649, C149, $D$2:$D$649, D149, $E$2:$E$649, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8530,11 +8528,11 @@
         <v>9470</v>
       </c>
       <c r="M150" s="17">
-        <f>ABS((D150*E150)-L150)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N150" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B150, $C$2:$C$649, C150, $D$2:$D$649, D150, $E$2:$E$649, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8568,7 +8566,7 @@
       </c>
       <c r="J151" s="32"/>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B151, $C$2:$C$649, C151, $D$2:$D$649, D151, $E$2:$E$649, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8614,7 +8612,7 @@
         <v>500</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B152, $C$2:$C$649, C152, $D$2:$D$649, D152, $E$2:$E$649, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O152" s="37" t="s">
@@ -8654,7 +8652,7 @@
         <v>117</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B153, $C$2:$C$649, C153, $D$2:$D$649, D153, $E$2:$E$649, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8688,7 +8686,7 @@
       </c>
       <c r="J154" s="32"/>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B154, $C$2:$C$649, C154, $D$2:$D$649, D154, $E$2:$E$649, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P154" s="27"/>
@@ -8735,7 +8733,7 @@
         <v>34175</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B155, $C$2:$C$649, C155, $D$2:$D$649, D155, $E$2:$E$649, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8769,7 +8767,7 @@
       </c>
       <c r="J156" s="32"/>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B156, $C$2:$C$649, C156, $D$2:$D$649, D156, $E$2:$E$649, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8815,7 +8813,7 @@
         <v>18350</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B157, $C$2:$C$649, C157, $D$2:$D$649, D157, $E$2:$E$649, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8849,7 +8847,7 @@
       </c>
       <c r="J158" s="32"/>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B158, $C$2:$C$649, C158, $D$2:$D$649, D158, $E$2:$E$649, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8895,7 +8893,7 @@
         <v>300</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B159, $C$2:$C$649, C159, $D$2:$D$649, D159, $E$2:$E$649, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="27"/>
@@ -8935,7 +8933,7 @@
       <c r="L160" s="17"/>
       <c r="M160" s="17"/>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B160, $C$2:$C$649, C160, $D$2:$D$649, D160, $E$2:$E$649, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="36" t="s">
@@ -8985,7 +8983,7 @@
         <v>646</v>
       </c>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B161, $C$2:$C$649, C161, $D$2:$D$649, D161, $E$2:$E$649, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="36" t="s">
@@ -9024,7 +9022,7 @@
         <v>117</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B162, $C$2:$C$649, C162, $D$2:$D$649, D162, $E$2:$E$649, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9070,7 +9068,7 @@
         <v>504.5</v>
       </c>
       <c r="N163" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B163, $C$2:$C$649, C163, $D$2:$D$649, D163, $E$2:$E$649, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O163" s="36" t="s">
@@ -9120,7 +9118,7 @@
         <v>545</v>
       </c>
       <c r="N164" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B164, $C$2:$C$649, C164, $D$2:$D$649, D164, $E$2:$E$649, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O164" s="36" t="s">
@@ -9160,7 +9158,7 @@
         <v>116</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B165, $C$2:$C$649, C165, $D$2:$D$649, D165, $E$2:$E$649, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9206,7 +9204,7 @@
         <v>260</v>
       </c>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B166, $C$2:$C$649, C166, $D$2:$D$649, D166, $E$2:$E$649, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9252,7 +9250,7 @@
         <v>395</v>
       </c>
       <c r="N167" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B167, $C$2:$C$649, C167, $D$2:$D$649, D167, $E$2:$E$649, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O167" s="36" t="s">
@@ -9302,7 +9300,7 @@
         <v>250</v>
       </c>
       <c r="N168" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B168, $C$2:$C$649, C168, $D$2:$D$649, D168, $E$2:$E$649, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O168" s="36" t="s">
@@ -9352,7 +9350,7 @@
         <v>300</v>
       </c>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B169, $C$2:$C$649, C169, $D$2:$D$649, D169, $E$2:$E$649, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9386,7 +9384,7 @@
       </c>
       <c r="J170" s="32"/>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B170, $C$2:$C$649, C170, $D$2:$D$649, D170, $E$2:$E$649, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9422,7 +9420,7 @@
         <v>116</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B171, $C$2:$C$649, C171, $D$2:$D$649, D171, $E$2:$E$649, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9456,7 +9454,7 @@
       </c>
       <c r="J172" s="32"/>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B172, $C$2:$C$649, C172, $D$2:$D$649, D172, $E$2:$E$649, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O172" s="36" t="s">
@@ -9506,7 +9504,7 @@
         <v>300</v>
       </c>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B173, $C$2:$C$649, C173, $D$2:$D$649, D173, $E$2:$E$649, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9552,7 +9550,7 @@
         <v>650</v>
       </c>
       <c r="N174" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B174, $C$2:$C$649, C174, $D$2:$D$649, D174, $E$2:$E$649, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P174" s="27"/>
@@ -9599,7 +9597,7 @@
         <v>450</v>
       </c>
       <c r="N175" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B175, $C$2:$C$649, C175, $D$2:$D$649, D175, $E$2:$E$649, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P175"/>
@@ -9634,7 +9632,7 @@
       </c>
       <c r="J176" s="32"/>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B176, $C$2:$C$649, C176, $D$2:$D$649, D176, $E$2:$E$649, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P176" s="27"/>
@@ -9681,7 +9679,7 @@
         <v>300</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B177, $C$2:$C$649, C177, $D$2:$D$649, D177, $E$2:$E$649, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="36" t="s">
@@ -9720,7 +9718,7 @@
         <v>117</v>
       </c>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B178, $C$2:$C$649, C178, $D$2:$D$649, D178, $E$2:$E$649, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9756,7 +9754,7 @@
         <v>54</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B179, $C$2:$C$649, C179, $D$2:$D$649, D179, $E$2:$E$649, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9802,7 +9800,7 @@
         <v>275</v>
       </c>
       <c r="N180" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B180, $C$2:$C$649, C180, $D$2:$D$649, D180, $E$2:$E$649, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -9848,7 +9846,7 @@
         <v>225</v>
       </c>
       <c r="N181" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B181, $C$2:$C$649, C181, $D$2:$D$649, D181, $E$2:$E$649, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -9884,7 +9882,7 @@
         <v>117</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B182, $C$2:$C$649, C182, $D$2:$D$649, D182, $E$2:$E$649, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9930,7 +9928,7 @@
         <v>300</v>
       </c>
       <c r="N183" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B183, $C$2:$C$649, C183, $D$2:$D$649, D183, $E$2:$E$649, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O183"/>
@@ -9968,7 +9966,7 @@
         <v>116</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B184, $C$2:$C$649, C184, $D$2:$D$649, D184, $E$2:$E$649, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10014,7 +10012,7 @@
         <v>300</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B185, $C$2:$C$649, C185, $D$2:$D$649, D185, $E$2:$E$649, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10060,7 +10058,7 @@
         <v>501</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B186, $C$2:$C$649, C186, $D$2:$D$649, D186, $E$2:$E$649, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O186" s="36" t="s">
@@ -10102,7 +10100,7 @@
       <c r="L187" s="16"/>
       <c r="M187" s="16"/>
       <c r="N187" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B187, $C$2:$C$649, C187, $D$2:$D$649, D187, $E$2:$E$649, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O187"/>
@@ -10139,7 +10137,7 @@
         <v>116</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B188, $C$2:$C$649, C188, $D$2:$D$649, D188, $E$2:$E$649, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10175,7 +10173,7 @@
         <v>117</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B189, $C$2:$C$649, C189, $D$2:$D$649, D189, $E$2:$E$649, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O189" s="27"/>
@@ -10210,7 +10208,7 @@
       </c>
       <c r="J190" s="32"/>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B190, $C$2:$C$649, C190, $D$2:$D$649, D190, $E$2:$E$649, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10244,7 +10242,7 @@
       </c>
       <c r="J191" s="32"/>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B191, $C$2:$C$649, C191, $D$2:$D$649, D191, $E$2:$E$649, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10280,7 +10278,7 @@
         <v>117</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B192, $C$2:$C$649, C192, $D$2:$D$649, D192, $E$2:$E$649, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="27"/>
@@ -10323,11 +10321,11 @@
         <v>3810</v>
       </c>
       <c r="M193" s="17">
-        <f>ABS((D193*E193)-L193)</f>
+        <f t="shared" ref="M193:M198" si="7">ABS((D193*E193)-L193)</f>
         <v>300</v>
       </c>
       <c r="N193" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B193, $C$2:$C$649, C193, $D$2:$D$649, D193, $E$2:$E$649, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10369,11 +10367,11 @@
         <v>3869</v>
       </c>
       <c r="M194" s="17">
-        <f>ABS((D194*E194)-L194)</f>
+        <f t="shared" si="7"/>
         <v>376</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B194, $C$2:$C$649, C194, $D$2:$D$649, D194, $E$2:$E$649, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="8">IF(COUNTIFS( $B$2:$B$649, B194, $C$2:$C$649, C194, $D$2:$D$649, D194, $E$2:$E$649, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10415,11 +10413,11 @@
         <v>10400</v>
       </c>
       <c r="M195" s="17">
-        <f>ABS((D195*E195)-L195)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B195, $C$2:$C$649, C195, $D$2:$D$649, D195, $E$2:$E$649, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10461,11 +10459,11 @@
         <v>5520</v>
       </c>
       <c r="M196" s="25">
-        <f>ABS((D196*E196)-L196)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N196" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B196, $C$2:$C$649, C196, $D$2:$D$649, D196, $E$2:$E$649, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O196" s="36" t="s">
@@ -10510,11 +10508,11 @@
         <v>2657</v>
       </c>
       <c r="M197" s="25">
-        <f>ABS((D197*E197)-L197)</f>
+        <f t="shared" si="7"/>
         <v>253</v>
       </c>
       <c r="N197" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B197, $C$2:$C$649, C197, $D$2:$D$649, D197, $E$2:$E$649, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
       <c r="O197" s="36" t="s">
@@ -10559,11 +10557,11 @@
         <v>2554.5</v>
       </c>
       <c r="M198" s="25">
-        <f>ABS((D198*E198)-L198)</f>
+        <f t="shared" si="7"/>
         <v>355.5</v>
       </c>
       <c r="N198" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B198, $C$2:$C$649, C198, $D$2:$D$649, D198, $E$2:$E$649, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
       <c r="O198" s="36" t="s">
@@ -10603,7 +10601,7 @@
       <c r="L199" s="17"/>
       <c r="M199" s="17"/>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B199, $C$2:$C$649, C199, $D$2:$D$649, D199, $E$2:$E$649, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="10"/>
@@ -10644,7 +10642,7 @@
       <c r="L200" s="16"/>
       <c r="M200" s="16"/>
       <c r="N200" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B200, $C$2:$C$649, C200, $D$2:$D$649, D200, $E$2:$E$649, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10680,7 +10678,7 @@
         <v>117</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B201, $C$2:$C$649, C201, $D$2:$D$649, D201, $E$2:$E$649, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10726,7 +10724,7 @@
         <v>800</v>
       </c>
       <c r="N202" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B202, $C$2:$C$649, C202, $D$2:$D$649, D202, $E$2:$E$649, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10772,7 +10770,7 @@
         <v>650</v>
       </c>
       <c r="N203" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B203, $C$2:$C$649, C203, $D$2:$D$649, D203, $E$2:$E$649, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P203" s="27"/>
@@ -10807,7 +10805,7 @@
       </c>
       <c r="J204" s="32"/>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B204, $C$2:$C$649, C204, $D$2:$D$649, D204, $E$2:$E$649, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10853,7 +10851,7 @@
         <v>290</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B205, $C$2:$C$649, C205, $D$2:$D$649, D205, $E$2:$E$649, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10899,7 +10897,7 @@
         <v>300</v>
       </c>
       <c r="N206" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B206, $C$2:$C$649, C206, $D$2:$D$649, D206, $E$2:$E$649, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="27"/>
@@ -10947,7 +10945,7 @@
         <v>188</v>
       </c>
       <c r="N207" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B207, $C$2:$C$649, C207, $D$2:$D$649, D207, $E$2:$E$649, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="27"/>
@@ -10995,7 +10993,7 @@
         <v>300</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B208, $C$2:$C$649, C208, $D$2:$D$649, D208, $E$2:$E$649, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11041,7 +11039,7 @@
         <v>268</v>
       </c>
       <c r="N209" s="58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B209, $C$2:$C$649, C209, $D$2:$D$649, D209, $E$2:$E$649, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O209" s="22"/>
@@ -11079,7 +11077,7 @@
       </c>
       <c r="J210" s="32"/>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B210, $C$2:$C$649, C210, $D$2:$D$649, D210, $E$2:$E$649, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O210" s="22"/>
@@ -11114,7 +11112,7 @@
       </c>
       <c r="J211" s="32"/>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B211, $C$2:$C$649, C211, $D$2:$D$649, D211, $E$2:$E$649, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11150,7 +11148,7 @@
         <v>117</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B212, $C$2:$C$649, C212, $D$2:$D$649, D212, $E$2:$E$649, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11196,7 +11194,7 @@
         <v>527.5</v>
       </c>
       <c r="N213" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B213, $C$2:$C$649, C213, $D$2:$D$649, D213, $E$2:$E$649, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11237,7 +11235,7 @@
       <c r="L214" s="25"/>
       <c r="M214" s="25"/>
       <c r="N214" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B214, $C$2:$C$649, C214, $D$2:$D$649, D214, $E$2:$E$649, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="27"/>
@@ -11275,7 +11273,7 @@
         <v>117</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B215, $C$2:$C$649, C215, $D$2:$D$649, D215, $E$2:$E$649, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="27"/>
@@ -11322,7 +11320,7 @@
         <v>650</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B216, $C$2:$C$649, C216, $D$2:$D$649, D216, $E$2:$E$649, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O216" s="27"/>
@@ -11369,7 +11367,7 @@
         <v>250</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B217, $C$2:$C$649, C217, $D$2:$D$649, D217, $E$2:$E$649, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11415,7 +11413,7 @@
         <v>300</v>
       </c>
       <c r="N218" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B218, $C$2:$C$649, C218, $D$2:$D$649, D218, $E$2:$E$649, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O218" s="10"/>
@@ -11463,7 +11461,7 @@
         <v>275</v>
       </c>
       <c r="N219" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B219, $C$2:$C$649, C219, $D$2:$D$649, D219, $E$2:$E$649, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O219" s="10"/>
@@ -11499,7 +11497,7 @@
       </c>
       <c r="J220" s="32"/>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B220, $C$2:$C$649, C220, $D$2:$D$649, D220, $E$2:$E$649, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11538,7 +11536,7 @@
       <c r="L221" s="16"/>
       <c r="M221" s="16"/>
       <c r="N221" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B221, $C$2:$C$649, C221, $D$2:$D$649, D221, $E$2:$E$649, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="10"/>
@@ -11586,7 +11584,7 @@
         <v>500</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B222, $C$2:$C$649, C222, $D$2:$D$649, D222, $E$2:$E$649, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11632,7 +11630,7 @@
         <v>360</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B223, $C$2:$C$649, C223, $D$2:$D$649, D223, $E$2:$E$649, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O223" s="10"/>
@@ -11673,7 +11671,7 @@
       <c r="L224" s="17"/>
       <c r="M224" s="17"/>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B224, $C$2:$C$649, C224, $D$2:$D$649, D224, $E$2:$E$649, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O224" s="10"/>
@@ -11711,7 +11709,7 @@
         <v>116</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B225, $C$2:$C$649, C225, $D$2:$D$649, D225, $E$2:$E$649, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P225" s="27"/>
@@ -11758,7 +11756,7 @@
         <v>320</v>
       </c>
       <c r="N226" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B226, $C$2:$C$649, C226, $D$2:$D$649, D226, $E$2:$E$649, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O226" s="27"/>
@@ -11806,7 +11804,7 @@
         <v>448</v>
       </c>
       <c r="N227" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B227, $C$2:$C$649, C227, $D$2:$D$649, D227, $E$2:$E$649, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O227" s="27"/>
@@ -11847,7 +11845,7 @@
       <c r="L228" s="17"/>
       <c r="M228" s="17"/>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B228, $C$2:$C$649, C228, $D$2:$D$649, D228, $E$2:$E$649, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O228" s="10"/>
@@ -11895,7 +11893,7 @@
         <v>280</v>
       </c>
       <c r="N229" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B229, $C$2:$C$649, C229, $D$2:$D$649, D229, $E$2:$E$649, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O229" s="10"/>
@@ -11943,7 +11941,7 @@
         <v>500</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B230, $C$2:$C$649, C230, $D$2:$D$649, D230, $E$2:$E$649, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11977,7 +11975,7 @@
       </c>
       <c r="J231" s="32"/>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B231, $C$2:$C$649, C231, $D$2:$D$649, D231, $E$2:$E$649, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12023,7 +12021,7 @@
         <v>250</v>
       </c>
       <c r="N232" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B232, $C$2:$C$649, C232, $D$2:$D$649, D232, $E$2:$E$649, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12069,7 +12067,7 @@
         <v>150</v>
       </c>
       <c r="N233" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B233, $C$2:$C$649, C233, $D$2:$D$649, D233, $E$2:$E$649, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -12115,7 +12113,7 @@
         <v>250</v>
       </c>
       <c r="N234" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B234, $C$2:$C$649, C234, $D$2:$D$649, D234, $E$2:$E$649, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -12149,7 +12147,7 @@
       </c>
       <c r="J235" s="32"/>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B235, $C$2:$C$649, C235, $D$2:$D$649, D235, $E$2:$E$649, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12195,7 +12193,7 @@
         <v>500</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B236, $C$2:$C$649, C236, $D$2:$D$649, D236, $E$2:$E$649, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12231,7 +12229,7 @@
         <v>54</v>
       </c>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B237, $C$2:$C$649, C237, $D$2:$D$649, D237, $E$2:$E$649, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12277,7 +12275,7 @@
         <v>300</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B238, $C$2:$C$649, C238, $D$2:$D$649, D238, $E$2:$E$649, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12316,7 +12314,7 @@
       <c r="L239" s="17"/>
       <c r="M239" s="17"/>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B239, $C$2:$C$649, C239, $D$2:$D$649, D239, $E$2:$E$649, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O239" s="10"/>
@@ -12364,7 +12362,7 @@
         <v>816</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B240, $C$2:$C$649, C240, $D$2:$D$649, D240, $E$2:$E$649, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O240" s="10"/>
@@ -12402,7 +12400,7 @@
         <v>117</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B241, $C$2:$C$649, C241, $D$2:$D$649, D241, $E$2:$E$649, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12448,7 +12446,7 @@
         <v>400</v>
       </c>
       <c r="N242" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B242, $C$2:$C$649, C242, $D$2:$D$649, D242, $E$2:$E$649, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12484,7 +12482,7 @@
         <v>117</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B243, $C$2:$C$649, C243, $D$2:$D$649, D243, $E$2:$E$649, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12530,7 +12528,7 @@
         <v>800</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B244, $C$2:$C$649, C244, $D$2:$D$649, D244, $E$2:$E$649, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O244" s="36" t="s">
@@ -12579,7 +12577,7 @@
         <v>500</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B245, $C$2:$C$649, C245, $D$2:$D$649, D245, $E$2:$E$649, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12613,7 +12611,7 @@
       </c>
       <c r="J246" s="32"/>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B246, $C$2:$C$649, C246, $D$2:$D$649, D246, $E$2:$E$649, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12647,7 +12645,7 @@
       </c>
       <c r="J247" s="32"/>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B247, $C$2:$C$649, C247, $D$2:$D$649, D247, $E$2:$E$649, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O247" s="27"/>
@@ -12687,7 +12685,7 @@
         <v>144</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B248, $C$2:$C$649, C248, $D$2:$D$649, D248, $E$2:$E$649, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12721,7 +12719,7 @@
       </c>
       <c r="J249" s="32"/>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B249, $C$2:$C$649, C249, $D$2:$D$649, D249, $E$2:$E$649, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P249" s="27"/>
@@ -12768,7 +12766,7 @@
         <v>260</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B250, $C$2:$C$649, C250, $D$2:$D$649, D250, $E$2:$E$649, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12814,7 +12812,7 @@
         <v>48320</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B251, $C$2:$C$649, C251, $D$2:$D$649, D251, $E$2:$E$649, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O251" s="36" t="s">
@@ -12853,7 +12851,7 @@
         <v>116</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B252, $C$2:$C$649, C252, $D$2:$D$649, D252, $E$2:$E$649, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12899,7 +12897,7 @@
         <v>370</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B253, $C$2:$C$649, C253, $D$2:$D$649, D253, $E$2:$E$649, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P253" s="27"/>
@@ -12946,7 +12944,7 @@
         <v>300</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B254, $C$2:$C$649, C254, $D$2:$D$649, D254, $E$2:$E$649, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="36" t="s">
@@ -12996,7 +12994,7 @@
         <v>140</v>
       </c>
       <c r="N255" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B255, $C$2:$C$649, C255, $D$2:$D$649, D255, $E$2:$E$649, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
       <c r="P255" s="27"/>
@@ -13043,7 +13041,7 @@
         <v>300</v>
       </c>
       <c r="N256" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B256, $C$2:$C$649, C256, $D$2:$D$649, D256, $E$2:$E$649, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -13077,7 +13075,7 @@
       </c>
       <c r="J257" s="32"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B257, $C$2:$C$649, C257, $D$2:$D$649, D257, $E$2:$E$649, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13123,7 +13121,7 @@
         <v>450</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B258, $C$2:$C$649, C258, $D$2:$D$649, D258, $E$2:$E$649, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N316" si="9">IF(COUNTIFS( $B$2:$B$649, B258, $C$2:$C$649, C258, $D$2:$D$649, D258, $E$2:$E$649, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13169,7 +13167,7 @@
         <v>290</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B259, $C$2:$C$649, C259, $D$2:$D$649, D259, $E$2:$E$649, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13215,7 +13213,7 @@
         <v>250</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B260, $C$2:$C$649, C260, $D$2:$D$649, D260, $E$2:$E$649, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P260" s="27"/>
@@ -13262,7 +13260,7 @@
         <v>1000</v>
       </c>
       <c r="N261" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B261, $C$2:$C$649, C261, $D$2:$D$649, D261, $E$2:$E$649, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13299,7 +13297,7 @@
       <c r="L262" s="17"/>
       <c r="M262" s="17"/>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B262, $C$2:$C$649, C262, $D$2:$D$649, D262, $E$2:$E$649, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O262" s="10"/>
@@ -13347,7 +13345,7 @@
         <v>47900</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B263, $C$2:$C$649, C263, $D$2:$D$649, D263, $E$2:$E$649, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O263" s="36" t="s">
@@ -13389,7 +13387,7 @@
       <c r="L264" s="17"/>
       <c r="M264" s="17"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B264, $C$2:$C$649, C264, $D$2:$D$649, D264, $E$2:$E$649, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O264" s="10"/>
@@ -13437,7 +13435,7 @@
         <v>300</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B265, $C$2:$C$649, C265, $D$2:$D$649, D265, $E$2:$E$649, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13483,7 +13481,7 @@
         <v>650</v>
       </c>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B266, $C$2:$C$649, C266, $D$2:$D$649, D266, $E$2:$E$649, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O266" s="36" t="s">
@@ -13532,7 +13530,7 @@
         <v>495</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B267, $C$2:$C$649, C267, $D$2:$D$649, D267, $E$2:$E$649, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O267" s="36" t="s">
@@ -13571,7 +13569,7 @@
         <v>116</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B268, $C$2:$C$649, C268, $D$2:$D$649, D268, $E$2:$E$649, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13617,7 +13615,7 @@
         <v>300</v>
       </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B269, $C$2:$C$649, C269, $D$2:$D$649, D269, $E$2:$E$649, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13651,7 +13649,7 @@
       </c>
       <c r="J270" s="32"/>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B270, $C$2:$C$649, C270, $D$2:$D$649, D270, $E$2:$E$649, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O270" s="27"/>
@@ -13688,7 +13686,7 @@
         <v>116</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B271, $C$2:$C$649, C271, $D$2:$D$649, D271, $E$2:$E$649, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13734,7 +13732,7 @@
         <v>300</v>
       </c>
       <c r="N272" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B272, $C$2:$C$649, C272, $D$2:$D$649, D272, $E$2:$E$649, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O272" s="36" t="s">
@@ -13784,7 +13782,7 @@
         <v>650</v>
       </c>
       <c r="N273" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B273, $C$2:$C$649, C273, $D$2:$D$649, D273, $E$2:$E$649, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O273"/>
@@ -13820,7 +13818,7 @@
       </c>
       <c r="J274" s="32"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B274, $C$2:$C$649, C274, $D$2:$D$649, D274, $E$2:$E$649, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13856,7 +13854,7 @@
         <v>116</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B275, $C$2:$C$649, C275, $D$2:$D$649, D275, $E$2:$E$649, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13902,7 +13900,7 @@
         <v>1800</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B276, $C$2:$C$649, C276, $D$2:$D$649, D276, $E$2:$E$649, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13936,7 +13934,7 @@
       </c>
       <c r="J277" s="32"/>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B277, $C$2:$C$649, C277, $D$2:$D$649, D277, $E$2:$E$649, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13975,7 +13973,7 @@
       <c r="L278" s="16"/>
       <c r="M278" s="16"/>
       <c r="N278" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B278, $C$2:$C$649, C278, $D$2:$D$649, D278, $E$2:$E$649, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O278"/>
@@ -14022,7 +14020,7 @@
         <v>47480</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B279, $C$2:$C$649, C279, $D$2:$D$649, D279, $E$2:$E$649, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14068,7 +14066,7 @@
         <v>420</v>
       </c>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B280, $C$2:$C$649, C280, $D$2:$D$649, D280, $E$2:$E$649, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14114,7 +14112,7 @@
         <v>340</v>
       </c>
       <c r="N281" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B281, $C$2:$C$649, C281, $D$2:$D$649, D281, $E$2:$E$649, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14160,7 +14158,7 @@
         <v>450</v>
       </c>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B282, $C$2:$C$649, C282, $D$2:$D$649, D282, $E$2:$E$649, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14196,7 +14194,7 @@
         <v>116</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B283, $C$2:$C$649, C283, $D$2:$D$649, D283, $E$2:$E$649, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14242,7 +14240,7 @@
         <v>300</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B284, $C$2:$C$649, C284, $D$2:$D$649, D284, $E$2:$E$649, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14288,7 +14286,7 @@
         <v>250</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B285, $C$2:$C$649, C285, $D$2:$D$649, D285, $E$2:$E$649, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14334,7 +14332,7 @@
         <v>300</v>
       </c>
       <c r="N286" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B286, $C$2:$C$649, C286, $D$2:$D$649, D286, $E$2:$E$649, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14370,7 +14368,7 @@
         <v>116</v>
       </c>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B287, $C$2:$C$649, C287, $D$2:$D$649, D287, $E$2:$E$649, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14406,7 +14404,7 @@
         <v>116</v>
       </c>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B288, $C$2:$C$649, C288, $D$2:$D$649, D288, $E$2:$E$649, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14452,7 +14450,7 @@
         <v>300</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B289, $C$2:$C$649, C289, $D$2:$D$649, D289, $E$2:$E$649, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14488,7 +14486,7 @@
         <v>116</v>
       </c>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B290, $C$2:$C$649, C290, $D$2:$D$649, D290, $E$2:$E$649, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14529,7 +14527,7 @@
       <c r="L291" s="16"/>
       <c r="M291" s="16"/>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B291, $C$2:$C$649, C291, $D$2:$D$649, D291, $E$2:$E$649, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14575,7 +14573,7 @@
         <v>480</v>
       </c>
       <c r="N292" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B292, $C$2:$C$649, C292, $D$2:$D$649, D292, $E$2:$E$649, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14611,7 +14609,7 @@
         <v>152</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B293, $C$2:$C$649, C293, $D$2:$D$649, D293, $E$2:$E$649, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14647,7 +14645,7 @@
         <v>117</v>
       </c>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B294, $C$2:$C$649, C294, $D$2:$D$649, D294, $E$2:$E$649, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14693,7 +14691,7 @@
         <v>250</v>
       </c>
       <c r="N295" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B295, $C$2:$C$649, C295, $D$2:$D$649, D295, $E$2:$E$649, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14727,7 +14725,7 @@
       </c>
       <c r="J296" s="32"/>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B296, $C$2:$C$649, C296, $D$2:$D$649, D296, $E$2:$E$649, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14773,7 +14771,7 @@
         <v>285</v>
       </c>
       <c r="N297" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B297, $C$2:$C$649, C297, $D$2:$D$649, D297, $E$2:$E$649, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14819,7 +14817,7 @@
         <v>726</v>
       </c>
       <c r="N298" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B298, $C$2:$C$649, C298, $D$2:$D$649, D298, $E$2:$E$649, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14855,7 +14853,7 @@
         <v>116</v>
       </c>
       <c r="N299" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B299, $C$2:$C$649, C299, $D$2:$D$649, D299, $E$2:$E$649, E299) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14889,7 +14887,7 @@
       </c>
       <c r="J300" s="32"/>
       <c r="N300" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B300, $C$2:$C$649, C300, $D$2:$D$649, D300, $E$2:$E$649, E300) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14925,7 +14923,7 @@
         <v>117</v>
       </c>
       <c r="N301" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B301, $C$2:$C$649, C301, $D$2:$D$649, D301, $E$2:$E$649, E301) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14971,7 +14969,7 @@
         <v>275</v>
       </c>
       <c r="N302" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B302, $C$2:$C$649, C302, $D$2:$D$649, D302, $E$2:$E$649, E302) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15005,7 +15003,7 @@
       </c>
       <c r="J303" s="32"/>
       <c r="N303" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B303, $C$2:$C$649, C303, $D$2:$D$649, D303, $E$2:$E$649, E303) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15051,7 +15049,7 @@
         <v>250</v>
       </c>
       <c r="N304" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B304, $C$2:$C$649, C304, $D$2:$D$649, D304, $E$2:$E$649, E304) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P304" s="27"/>
@@ -15086,7 +15084,7 @@
       </c>
       <c r="J305" s="32"/>
       <c r="N305" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B305, $C$2:$C$649, C305, $D$2:$D$649, D305, $E$2:$E$649, E305) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15122,7 +15120,7 @@
         <v>54</v>
       </c>
       <c r="N306" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B306, $C$2:$C$649, C306, $D$2:$D$649, D306, $E$2:$E$649, E306) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15156,7 +15154,7 @@
       </c>
       <c r="J307" s="32"/>
       <c r="N307" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B307, $C$2:$C$649, C307, $D$2:$D$649, D307, $E$2:$E$649, E307) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15202,7 +15200,7 @@
         <v>300</v>
       </c>
       <c r="N308" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B308, $C$2:$C$649, C308, $D$2:$D$649, D308, $E$2:$E$649, E308) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15248,7 +15246,7 @@
         <v>235</v>
       </c>
       <c r="N309" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B309, $C$2:$C$649, C309, $D$2:$D$649, D309, $E$2:$E$649, E309) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15284,7 +15282,7 @@
         <v>117</v>
       </c>
       <c r="N310" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B310, $C$2:$C$649, C310, $D$2:$D$649, D310, $E$2:$E$649, E310) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15320,7 +15318,7 @@
         <v>117</v>
       </c>
       <c r="N311" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B311, $C$2:$C$649, C311, $D$2:$D$649, D311, $E$2:$E$649, E311) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15354,7 +15352,7 @@
       </c>
       <c r="J312" s="32"/>
       <c r="N312" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B312, $C$2:$C$649, C312, $D$2:$D$649, D312, $E$2:$E$649, E312) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15400,7 +15398,7 @@
         <v>250</v>
       </c>
       <c r="N313" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B313, $C$2:$C$649, C313, $D$2:$D$649, D313, $E$2:$E$649, E313) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15439,7 +15437,7 @@
       <c r="L314" s="25"/>
       <c r="M314" s="25"/>
       <c r="N314" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B314, $C$2:$C$649, C314, $D$2:$D$649, D314, $E$2:$E$649, E314) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O314" s="27"/>
@@ -15480,7 +15478,7 @@
       <c r="L315" s="25"/>
       <c r="M315" s="25"/>
       <c r="N315" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B315, $C$2:$C$649, C315, $D$2:$D$649, D315, $E$2:$E$649, E315) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O315" s="27"/>
@@ -15518,7 +15516,7 @@
         <v>116</v>
       </c>
       <c r="N316" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B316, $C$2:$C$649, C316, $D$2:$D$649, D316, $E$2:$E$649, E316) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22926,7 +22924,7 @@
         <v>3024.2</v>
       </c>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$875, B2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N9" si="2">IF(COUNTIFS( $B$2:$B$875, B2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -22950,15 +22948,15 @@
         <v>302</v>
       </c>
       <c r="K3" t="str">
-        <f t="shared" ref="K3" si="2">C3 &amp; " " &amp; D3 &amp; "*" &amp; E3 &amp; " :" &amp; A3</f>
+        <f t="shared" ref="K3" si="3">C3 &amp; " " &amp; D3 &amp; "*" &amp; E3 &amp; " :" &amp; A3</f>
         <v>S 10*1796 :16 OCT 2026 09:00:47 AM</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3" si="3">D3*E3</f>
+        <f t="shared" ref="L3" si="4">D3*E3</f>
         <v>17960</v>
       </c>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$875, B3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22982,15 +22980,15 @@
         <v>302</v>
       </c>
       <c r="K4" t="str">
-        <f t="shared" ref="K4:K7" si="4">C4 &amp; " " &amp; D4 &amp; "*" &amp; E4 &amp; " :" &amp; A4</f>
+        <f t="shared" ref="K4:K7" si="5">C4 &amp; " " &amp; D4 &amp; "*" &amp; E4 &amp; " :" &amp; A4</f>
         <v>S 50*833 :16 OCT 2026 02:36:36 PM</v>
       </c>
       <c r="L4">
-        <f t="shared" ref="L4:L7" si="5">D4*E4</f>
+        <f t="shared" ref="L4:L7" si="6">D4*E4</f>
         <v>41650</v>
       </c>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$875, B4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23014,15 +23012,15 @@
         <v>302</v>
       </c>
       <c r="K5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>S 10*773 :16 OCT 2026 09:00:45 AM</v>
       </c>
       <c r="L5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7730</v>
       </c>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$875, B5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -23046,15 +23044,15 @@
         <v>302</v>
       </c>
       <c r="K6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>S 5*710 :16 OCT 2026 09:00:46 AM</v>
       </c>
       <c r="L6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3550</v>
       </c>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$875, B6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -23078,15 +23076,15 @@
         <v>302</v>
       </c>
       <c r="K7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>S 30*283 :16 OCT 2026 02:18:12 PM</v>
       </c>
       <c r="L7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8490</v>
       </c>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$875, B7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23110,15 +23108,15 @@
         <v>302</v>
       </c>
       <c r="K8" t="str">
-        <f t="shared" ref="K8:K9" si="6">C8 &amp; " " &amp; D8 &amp; "*" &amp; E8 &amp; " :" &amp; A8</f>
+        <f t="shared" ref="K8:K9" si="7">C8 &amp; " " &amp; D8 &amp; "*" &amp; E8 &amp; " :" &amp; A8</f>
         <v>S 5*762 :16 OCT 2026 09:00:44 AM</v>
       </c>
       <c r="L8">
-        <f t="shared" ref="L8:L9" si="7">D8*E8</f>
+        <f t="shared" ref="L8:L9" si="8">D8*E8</f>
         <v>3810</v>
       </c>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$875, B8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -23142,15 +23140,15 @@
         <v>302</v>
       </c>
       <c r="K9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>S 5*690 :16 OCT 2026 09:00:35 AM</v>
       </c>
       <c r="L9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3450</v>
       </c>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$875, B9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -23265,7 +23263,7 @@
         <v>10880</v>
       </c>
       <c r="N2" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B2, $C$2:$C$649, C2, $D$2:$D$649, D2, $E$2:$E$649, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$649, B2, $C$2:$C$649, C2, $D$2:$D$649, D2, $E$2:$E$649, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -23313,7 +23311,7 @@
         <v>10680</v>
       </c>
       <c r="N3" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B3, $C$2:$C$649, C3, $D$2:$D$649, D3, $E$2:$E$649, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -23354,7 +23352,7 @@
       <c r="L4" s="16"/>
       <c r="M4" s="16"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B4, $C$2:$C$649, C4, $D$2:$D$649, D4, $E$2:$E$649, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23393,7 +23391,7 @@
       <c r="L5" s="16"/>
       <c r="M5" s="16"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B5, $C$2:$C$649, C5, $D$2:$D$649, D5, $E$2:$E$649, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23432,7 +23430,7 @@
       <c r="L6" s="16"/>
       <c r="M6" s="16"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B6, $C$2:$C$649, C6, $D$2:$D$649, D6, $E$2:$E$649, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="37" t="s">
@@ -23481,7 +23479,7 @@
         <v>264</v>
       </c>
       <c r="N7" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B7, $C$2:$C$649, C7, $D$2:$D$649, D7, $E$2:$E$649, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
@@ -23520,7 +23518,7 @@
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B8, $C$2:$C$649, C8, $D$2:$D$649, D8, $E$2:$E$649, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23562,7 +23560,7 @@
         <v>3156</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B9, $C$2:$C$649, C9, $D$2:$D$649, D9, $E$2:$E$649, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
@@ -23610,7 +23608,7 @@
         <v>240</v>
       </c>
       <c r="N10" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B10, $C$2:$C$649, C10, $D$2:$D$649, D10, $E$2:$E$649, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="10"/>
@@ -23649,7 +23647,7 @@
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B11, $C$2:$C$649, C11, $D$2:$D$649, D11, $E$2:$E$649, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23688,7 +23686,7 @@
       <c r="L12" s="16"/>
       <c r="M12" s="16"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B12, $C$2:$C$649, C12, $D$2:$D$649, D12, $E$2:$E$649, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23734,7 +23732,7 @@
         <v>295</v>
       </c>
       <c r="N13" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B13, $C$2:$C$649, C13, $D$2:$D$649, D13, $E$2:$E$649, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23773,7 +23771,7 @@
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B14, $C$2:$C$649, C14, $D$2:$D$649, D14, $E$2:$E$649, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14"/>
@@ -23814,7 +23812,7 @@
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B15, $C$2:$C$649, C15, $D$2:$D$649, D15, $E$2:$E$649, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15"/>
@@ -23853,7 +23851,7 @@
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B16, $C$2:$C$649, C16, $D$2:$D$649, D16, $E$2:$E$649, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16"/>
@@ -23901,7 +23899,7 @@
         <v>1300</v>
       </c>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B17, $C$2:$C$649, C17, $D$2:$D$649, D17, $E$2:$E$649, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23947,7 +23945,7 @@
         <v>700</v>
       </c>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B18, $C$2:$C$649, C18, $D$2:$D$649, D18, $E$2:$E$649, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="10"/>
@@ -23995,7 +23993,7 @@
         <v>450</v>
       </c>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B19, $C$2:$C$649, C19, $D$2:$D$649, D19, $E$2:$E$649, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24032,7 +24030,7 @@
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B20, $C$2:$C$649, C20, $D$2:$D$649, D20, $E$2:$E$649, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20"/>
@@ -24071,7 +24069,7 @@
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B21, $C$2:$C$649, C21, $D$2:$D$649, D21, $E$2:$E$649, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21"/>
@@ -24120,7 +24118,7 @@
         <v>448</v>
       </c>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B22, $C$2:$C$649, C22, $D$2:$D$649, D22, $E$2:$E$649, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24157,7 +24155,7 @@
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B23, $C$2:$C$649, C23, $D$2:$D$649, D23, $E$2:$E$649, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23"/>
@@ -24196,7 +24194,7 @@
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B24, $C$2:$C$649, C24, $D$2:$D$649, D24, $E$2:$E$649, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -24244,7 +24242,7 @@
         <v>250</v>
       </c>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B25, $C$2:$C$649, C25, $D$2:$D$649, D25, $E$2:$E$649, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24290,7 +24288,7 @@
         <v>360</v>
       </c>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B26, $C$2:$C$649, C26, $D$2:$D$649, D26, $E$2:$E$649, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24336,7 +24334,7 @@
         <v>800</v>
       </c>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B27, $C$2:$C$649, C27, $D$2:$D$649, D27, $E$2:$E$649, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27" s="10"/>
@@ -24375,7 +24373,7 @@
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B28, $C$2:$C$649, C28, $D$2:$D$649, D28, $E$2:$E$649, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
@@ -24414,7 +24412,7 @@
       <c r="L29" s="16"/>
       <c r="M29" s="16"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B29, $C$2:$C$649, C29, $D$2:$D$649, D29, $E$2:$E$649, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29"/>
@@ -24453,7 +24451,7 @@
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B30, $C$2:$C$649, C30, $D$2:$D$649, D30, $E$2:$E$649, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30"/>
@@ -24494,7 +24492,7 @@
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B31, $C$2:$C$649, C31, $D$2:$D$649, D31, $E$2:$E$649, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -24533,7 +24531,7 @@
       <c r="L32" s="16"/>
       <c r="M32" s="16"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B32, $C$2:$C$649, C32, $D$2:$D$649, D32, $E$2:$E$649, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
@@ -24581,7 +24579,7 @@
         <v>660</v>
       </c>
       <c r="N33" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B33, $C$2:$C$649, C33, $D$2:$D$649, D33, $E$2:$E$649, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24628,7 +24626,7 @@
         <v>540</v>
       </c>
       <c r="N34" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B34, $C$2:$C$649, C34, $D$2:$D$649, D34, $E$2:$E$649, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -24676,7 +24674,7 @@
         <v>300</v>
       </c>
       <c r="N35" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B35, $C$2:$C$649, C35, $D$2:$D$649, D35, $E$2:$E$649, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35" s="10"/>
@@ -24725,7 +24723,7 @@
         <v>225</v>
       </c>
       <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B36, $C$2:$C$649, C36, $D$2:$D$649, D36, $E$2:$E$649, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24764,7 +24762,7 @@
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B37, $C$2:$C$649, C37, $D$2:$D$649, D37, $E$2:$E$649, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -24805,7 +24803,7 @@
       <c r="L38" s="16"/>
       <c r="M38" s="16"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B38, $C$2:$C$649, C38, $D$2:$D$649, D38, $E$2:$E$649, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
@@ -24849,11 +24847,11 @@
         <v>8570</v>
       </c>
       <c r="M39" s="25">
-        <f t="shared" ref="M39:M44" si="0">ABS((D39*E39)-L39)</f>
+        <f t="shared" ref="M39:M44" si="1">ABS((D39*E39)-L39)</f>
         <v>50</v>
       </c>
       <c r="N39" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B39, $C$2:$C$649, C39, $D$2:$D$649, D39, $E$2:$E$649, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O39" s="27"/>
@@ -24897,11 +24895,11 @@
         <v>8670</v>
       </c>
       <c r="M40" s="25">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="N40" s="27" t="str">
         <f t="shared" si="0"/>
-        <v>150</v>
-      </c>
-      <c r="N40" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B40, $C$2:$C$649, C40, $D$2:$D$649, D40, $E$2:$E$649, E40) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O40" s="27"/>
@@ -24945,11 +24943,11 @@
         <v>8870</v>
       </c>
       <c r="M41" s="25">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+      <c r="N41" s="26" t="str">
         <f t="shared" si="0"/>
-        <v>350</v>
-      </c>
-      <c r="N41" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B41, $C$2:$C$649, C41, $D$2:$D$649, D41, $E$2:$E$649, E41) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O41" s="27"/>
@@ -24993,11 +24991,11 @@
         <v>8770</v>
       </c>
       <c r="M42" s="25">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="N42" s="26" t="str">
         <f t="shared" si="0"/>
-        <v>250</v>
-      </c>
-      <c r="N42" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B42, $C$2:$C$649, C42, $D$2:$D$649, D42, $E$2:$E$649, E42) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O42" s="27"/>
@@ -25041,11 +25039,11 @@
         <v>16740</v>
       </c>
       <c r="M43" s="17">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="N43" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="N43" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B43, $C$2:$C$649, C43, $D$2:$D$649, D43, $E$2:$E$649, E43) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O43" s="10"/>
@@ -25089,11 +25087,11 @@
         <v>4763</v>
       </c>
       <c r="M44" s="17">
+        <f t="shared" si="1"/>
+        <v>253</v>
+      </c>
+      <c r="N44" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>253</v>
-      </c>
-      <c r="N44" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B44, $C$2:$C$649, C44, $D$2:$D$649, D44, $E$2:$E$649, E44) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O44" s="10"/>
@@ -25132,7 +25130,7 @@
       <c r="L45" s="16"/>
       <c r="M45" s="16"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B45, $C$2:$C$649, C45, $D$2:$D$649, D45, $E$2:$E$649, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -25173,7 +25171,7 @@
       <c r="L46" s="61"/>
       <c r="M46" s="61"/>
       <c r="N46" s="53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B46, $C$2:$C$649, C46, $D$2:$D$649, D46, $E$2:$E$649, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46" s="53"/>
@@ -25221,7 +25219,7 @@
         <v>700</v>
       </c>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B47, $C$2:$C$649, C47, $D$2:$D$649, D47, $E$2:$E$649, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25258,7 +25256,7 @@
       <c r="L48" s="16"/>
       <c r="M48" s="16"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B48, $C$2:$C$649, C48, $D$2:$D$649, D48, $E$2:$E$649, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48"/>
@@ -25302,11 +25300,11 @@
         <v>8970</v>
       </c>
       <c r="M49" s="17">
-        <f t="shared" ref="M49:M56" si="1">ABS((D49*E49)-L49)</f>
+        <f t="shared" ref="M49:M56" si="2">ABS((D49*E49)-L49)</f>
         <v>250</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B49, $C$2:$C$649, C49, $D$2:$D$649, D49, $E$2:$E$649, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49" s="10"/>
@@ -25351,11 +25349,11 @@
         <v>8760</v>
       </c>
       <c r="M50" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>440</v>
       </c>
       <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B50, $C$2:$C$649, C50, $D$2:$D$649, D50, $E$2:$E$649, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50" s="10"/>
@@ -25399,11 +25397,11 @@
         <v>35560</v>
       </c>
       <c r="M51" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>720</v>
       </c>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B51, $C$2:$C$649, C51, $D$2:$D$649, D51, $E$2:$E$649, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25445,11 +25443,11 @@
         <v>18855</v>
       </c>
       <c r="M52" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B52, $C$2:$C$649, C52, $D$2:$D$649, D52, $E$2:$E$649, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="10"/>
@@ -25493,11 +25491,11 @@
         <v>32200</v>
       </c>
       <c r="M53" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>689.99999999999636</v>
       </c>
       <c r="N53" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B53, $C$2:$C$649, C53, $D$2:$D$649, D53, $E$2:$E$649, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25539,11 +25537,11 @@
         <v>20020</v>
       </c>
       <c r="M54" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>470</v>
       </c>
       <c r="N54" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B54, $C$2:$C$649, C54, $D$2:$D$649, D54, $E$2:$E$649, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25585,11 +25583,11 @@
         <v>14544</v>
       </c>
       <c r="M55" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>660</v>
       </c>
       <c r="N55" s="64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B55, $C$2:$C$649, C55, $D$2:$D$649, D55, $E$2:$E$649, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55" s="64"/>
@@ -25633,11 +25631,11 @@
         <v>14860</v>
       </c>
       <c r="M56" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B56, $C$2:$C$649, C56, $D$2:$D$649, D56, $E$2:$E$649, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25674,7 +25672,7 @@
       <c r="L57" s="16"/>
       <c r="M57" s="16"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B57, $C$2:$C$649, C57, $D$2:$D$649, D57, $E$2:$E$649, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -25717,7 +25715,7 @@
       <c r="L58" s="16"/>
       <c r="M58" s="16"/>
       <c r="N58" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B58, $C$2:$C$649, C58, $D$2:$D$649, D58, $E$2:$E$649, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -25756,7 +25754,7 @@
       <c r="L59" s="16"/>
       <c r="M59" s="16"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B59, $C$2:$C$649, C59, $D$2:$D$649, D59, $E$2:$E$649, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
@@ -25803,7 +25801,7 @@
         <v>400</v>
       </c>
       <c r="N60" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B60, $C$2:$C$649, C60, $D$2:$D$649, D60, $E$2:$E$649, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60" s="10"/>
@@ -25851,7 +25849,7 @@
         <v>400</v>
       </c>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B61, $C$2:$C$649, C61, $D$2:$D$649, D61, $E$2:$E$649, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61" s="10"/>
@@ -25892,7 +25890,7 @@
       <c r="L62" s="16"/>
       <c r="M62" s="16"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B62, $C$2:$C$649, C62, $D$2:$D$649, D62, $E$2:$E$649, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25931,7 +25929,7 @@
       <c r="L63" s="16"/>
       <c r="M63" s="16"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B63, $C$2:$C$649, C63, $D$2:$D$649, D63, $E$2:$E$649, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63"/>
@@ -25972,7 +25970,7 @@
       <c r="L64" s="16"/>
       <c r="M64" s="16"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B64, $C$2:$C$649, C64, $D$2:$D$649, D64, $E$2:$E$649, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -26021,7 +26019,7 @@
         <v>200</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B65, $C$2:$C$649, C65, $D$2:$D$649, D65, $E$2:$E$649, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26057,7 +26055,7 @@
         <v>117</v>
       </c>
       <c r="N66" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B66, $C$2:$C$649, C66, $D$2:$D$649, D66, $E$2:$E$649, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="3">IF(COUNTIFS( $B$2:$B$649, B66, $C$2:$C$649, C66, $D$2:$D$649, D66, $E$2:$E$649, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P66"/>
@@ -26097,7 +26095,7 @@
       <c r="L67" s="16"/>
       <c r="M67" s="16"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B67, $C$2:$C$649, C67, $D$2:$D$649, D67, $E$2:$E$649, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26144,7 +26142,7 @@
         <v>300</v>
       </c>
       <c r="N68" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B68, $C$2:$C$649, C68, $D$2:$D$649, D68, $E$2:$E$649, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="36" t="s">
@@ -26186,7 +26184,7 @@
       <c r="L69" s="16"/>
       <c r="M69" s="16"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B69, $C$2:$C$649, C69, $D$2:$D$649, D69, $E$2:$E$649, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
@@ -26234,7 +26232,7 @@
         <v>500</v>
       </c>
       <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B70, $C$2:$C$649, C70, $D$2:$D$649, D70, $E$2:$E$649, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26281,7 +26279,7 @@
         <v>300</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B71, $C$2:$C$649, C71, $D$2:$D$649, D71, $E$2:$E$649, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26327,7 +26325,7 @@
         <v>1200</v>
       </c>
       <c r="N72" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B72, $C$2:$C$649, C72, $D$2:$D$649, D72, $E$2:$E$649, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O72" s="36" t="s">
@@ -26369,7 +26367,7 @@
       <c r="L73" s="16"/>
       <c r="M73" s="16"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B73, $C$2:$C$649, C73, $D$2:$D$649, D73, $E$2:$E$649, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P73"/>
@@ -26409,7 +26407,7 @@
       <c r="L74" s="16"/>
       <c r="M74" s="16"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B74, $C$2:$C$649, C74, $D$2:$D$649, D74, $E$2:$E$649, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O74"/>
@@ -26457,7 +26455,7 @@
         <v>11409.000000000004</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B75, $C$2:$C$649, C75, $D$2:$D$649, D75, $E$2:$E$649, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P75"/>
@@ -26504,7 +26502,7 @@
         <v>612.5</v>
       </c>
       <c r="N76" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B76, $C$2:$C$649, C76, $D$2:$D$649, D76, $E$2:$E$649, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O76" s="27"/>
@@ -26552,7 +26550,7 @@
         <v>420</v>
       </c>
       <c r="N77" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B77, $C$2:$C$649, C77, $D$2:$D$649, D77, $E$2:$E$649, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O77" s="27"/>
@@ -26600,7 +26598,7 @@
         <v>200</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B78, $C$2:$C$649, C78, $D$2:$D$649, D78, $E$2:$E$649, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26637,7 +26635,7 @@
       <c r="L79" s="16"/>
       <c r="M79" s="16"/>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B79, $C$2:$C$649, C79, $D$2:$D$649, D79, $E$2:$E$649, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26683,7 +26681,7 @@
         <v>265</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B80, $C$2:$C$649, C80, $D$2:$D$649, D80, $E$2:$E$649, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26729,7 +26727,7 @@
         <v>1400</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B81, $C$2:$C$649, C81, $D$2:$D$649, D81, $E$2:$E$649, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="36" t="s">
@@ -26778,7 +26776,7 @@
         <v>300</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B82, $C$2:$C$649, C82, $D$2:$D$649, D82, $E$2:$E$649, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26817,7 +26815,7 @@
       <c r="L83" s="16"/>
       <c r="M83" s="16"/>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B83, $C$2:$C$649, C83, $D$2:$D$649, D83, $E$2:$E$649, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26854,7 +26852,7 @@
       <c r="L84" s="16"/>
       <c r="M84" s="16"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B84, $C$2:$C$649, C84, $D$2:$D$649, D84, $E$2:$E$649, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26900,7 +26898,7 @@
         <v>1000</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B85, $C$2:$C$649, C85, $D$2:$D$649, D85, $E$2:$E$649, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26946,7 +26944,7 @@
         <v>390</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B86, $C$2:$C$649, C86, $D$2:$D$649, D86, $E$2:$E$649, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26992,7 +26990,7 @@
         <v>300</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B87, $C$2:$C$649, C87, $D$2:$D$649, D87, $E$2:$E$649, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27038,7 +27036,7 @@
         <v>14149.000000000004</v>
       </c>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B88, $C$2:$C$649, C88, $D$2:$D$649, D88, $E$2:$E$649, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="10"/>
@@ -27074,7 +27072,7 @@
       </c>
       <c r="J89" s="32"/>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B89, $C$2:$C$649, C89, $D$2:$D$649, D89, $E$2:$E$649, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27120,7 +27118,7 @@
         <v>274</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B90, $C$2:$C$649, C90, $D$2:$D$649, D90, $E$2:$E$649, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27157,7 +27155,7 @@
       <c r="L91" s="16"/>
       <c r="M91" s="16"/>
       <c r="N91" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B91, $C$2:$C$649, C91, $D$2:$D$649, D91, $E$2:$E$649, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O91" s="18"/>
@@ -27200,11 +27198,11 @@
         <v>12800</v>
       </c>
       <c r="M92" s="17">
-        <f t="shared" ref="M92:M97" si="2">ABS((D92*E92)-L92)</f>
+        <f t="shared" ref="M92:M97" si="4">ABS((D92*E92)-L92)</f>
         <v>650</v>
       </c>
       <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B92, $C$2:$C$649, C92, $D$2:$D$649, D92, $E$2:$E$649, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27246,11 +27244,11 @@
         <v>14310</v>
       </c>
       <c r="M93" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>660</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B93, $C$2:$C$649, C93, $D$2:$D$649, D93, $E$2:$E$649, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O93" s="10"/>
@@ -27294,11 +27292,11 @@
         <v>17700</v>
       </c>
       <c r="M94" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B94, $C$2:$C$649, C94, $D$2:$D$649, D94, $E$2:$E$649, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P94" s="22"/>
@@ -27341,11 +27339,11 @@
         <v>16755</v>
       </c>
       <c r="M95" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>295</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B95, $C$2:$C$649, C95, $D$2:$D$649, D95, $E$2:$E$649, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27387,11 +27385,11 @@
         <v>17920</v>
       </c>
       <c r="M96" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>516</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B96, $C$2:$C$649, C96, $D$2:$D$649, D96, $E$2:$E$649, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27433,11 +27431,11 @@
         <v>8220</v>
       </c>
       <c r="M97" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>360</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B97, $C$2:$C$649, C97, $D$2:$D$649, D97, $E$2:$E$649, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O97" s="36" t="s">
@@ -27477,7 +27475,7 @@
         <v>117</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B98, $C$2:$C$649, C98, $D$2:$D$649, D98, $E$2:$E$649, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27523,7 +27521,7 @@
         <v>300</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B99, $C$2:$C$649, C99, $D$2:$D$649, D99, $E$2:$E$649, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="P99" s="23"/>
@@ -27570,7 +27568,7 @@
         <v>300</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B100, $C$2:$C$649, C100, $D$2:$D$649, D100, $E$2:$E$649, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O100" s="10"/>
@@ -27618,7 +27616,7 @@
         <v>250</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B101, $C$2:$C$649, C101, $D$2:$D$649, D101, $E$2:$E$649, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="36" t="s">
@@ -27658,7 +27656,7 @@
       <c r="L102" s="16"/>
       <c r="M102" s="16"/>
       <c r="N102" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B102, $C$2:$C$649, C102, $D$2:$D$649, D102, $E$2:$E$649, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="23"/>
@@ -27698,7 +27696,7 @@
       <c r="L103" s="16"/>
       <c r="M103" s="16"/>
       <c r="N103" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B103, $C$2:$C$649, C103, $D$2:$D$649, D103, $E$2:$E$649, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27744,7 +27742,7 @@
         <v>1200</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B104, $C$2:$C$649, C104, $D$2:$D$649, D104, $E$2:$E$649, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="10"/>
@@ -27792,7 +27790,7 @@
         <v>650</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B105, $C$2:$C$649, C105, $D$2:$D$649, D105, $E$2:$E$649, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="36" t="s">
@@ -27842,7 +27840,7 @@
         <v>654.5</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B106, $C$2:$C$649, C106, $D$2:$D$649, D106, $E$2:$E$649, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O106" s="36" t="s">
@@ -27892,7 +27890,7 @@
         <v>18850</v>
       </c>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B107, $C$2:$C$649, C107, $D$2:$D$649, D107, $E$2:$E$649, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27938,7 +27936,7 @@
         <v>650</v>
       </c>
       <c r="N108" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B108, $C$2:$C$649, C108, $D$2:$D$649, D108, $E$2:$E$649, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27974,7 +27972,7 @@
         <v>117</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B109, $C$2:$C$649, C109, $D$2:$D$649, D109, $E$2:$E$649, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28010,7 +28008,7 @@
         <v>117</v>
       </c>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B110, $C$2:$C$649, C110, $D$2:$D$649, D110, $E$2:$E$649, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28052,11 +28050,11 @@
         <v>17040</v>
       </c>
       <c r="M111" s="17">
-        <f t="shared" ref="M111:M125" si="3">ABS((D111*E111)-L111)</f>
+        <f t="shared" ref="M111:M125" si="5">ABS((D111*E111)-L111)</f>
         <v>880</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B111, $C$2:$C$649, C111, $D$2:$D$649, D111, $E$2:$E$649, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O111" s="36" t="s">
@@ -28101,11 +28099,11 @@
         <v>8400</v>
       </c>
       <c r="M112" s="17">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+      <c r="N112" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>300</v>
-      </c>
-      <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B112, $C$2:$C$649, C112, $D$2:$D$649, D112, $E$2:$E$649, E112) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O112" s="36" t="s">
@@ -28150,11 +28148,11 @@
         <v>21900</v>
       </c>
       <c r="M113" s="17">
+        <f t="shared" si="5"/>
+        <v>500</v>
+      </c>
+      <c r="N113" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>500</v>
-      </c>
-      <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B113, $C$2:$C$649, C113, $D$2:$D$649, D113, $E$2:$E$649, E113) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -28196,11 +28194,11 @@
         <v>8420</v>
       </c>
       <c r="M114" s="17">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+      <c r="N114" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>300</v>
-      </c>
-      <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B114, $C$2:$C$649, C114, $D$2:$D$649, D114, $E$2:$E$649, E114) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -28242,11 +28240,11 @@
         <v>33950</v>
       </c>
       <c r="M115" s="17">
+        <f t="shared" si="5"/>
+        <v>850</v>
+      </c>
+      <c r="N115" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>850</v>
-      </c>
-      <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B115, $C$2:$C$649, C115, $D$2:$D$649, D115, $E$2:$E$649, E115) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -28288,11 +28286,11 @@
         <v>7578</v>
       </c>
       <c r="M116" s="25">
+        <f t="shared" si="5"/>
+        <v>294</v>
+      </c>
+      <c r="N116" s="26" t="str">
         <f t="shared" si="3"/>
-        <v>294</v>
-      </c>
-      <c r="N116" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B116, $C$2:$C$649, C116, $D$2:$D$649, D116, $E$2:$E$649, E116) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O116" s="10"/>
@@ -28336,11 +28334,11 @@
         <v>7578</v>
       </c>
       <c r="M117" s="25">
+        <f t="shared" si="5"/>
+        <v>294</v>
+      </c>
+      <c r="N117" s="27" t="str">
         <f t="shared" si="3"/>
-        <v>294</v>
-      </c>
-      <c r="N117" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B117, $C$2:$C$649, C117, $D$2:$D$649, D117, $E$2:$E$649, E117) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O117" s="10"/>
@@ -28384,11 +28382,11 @@
         <v>4968</v>
       </c>
       <c r="M118" s="25">
+        <f t="shared" si="5"/>
+        <v>280</v>
+      </c>
+      <c r="N118" s="27" t="str">
         <f t="shared" si="3"/>
-        <v>280</v>
-      </c>
-      <c r="N118" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B118, $C$2:$C$649, C118, $D$2:$D$649, D118, $E$2:$E$649, E118) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O118" s="27"/>
@@ -28433,11 +28431,11 @@
         <v>6900</v>
       </c>
       <c r="M119" s="17">
+        <f t="shared" si="5"/>
+        <v>444</v>
+      </c>
+      <c r="N119" t="str">
         <f t="shared" si="3"/>
-        <v>444</v>
-      </c>
-      <c r="N119" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B119, $C$2:$C$649, C119, $D$2:$D$649, D119, $E$2:$E$649, E119) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -28479,11 +28477,11 @@
         <v>17150</v>
       </c>
       <c r="M120" s="17">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+      <c r="N120" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>300</v>
-      </c>
-      <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B120, $C$2:$C$649, C120, $D$2:$D$649, D120, $E$2:$E$649, E120) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -28525,11 +28523,11 @@
         <v>9393.5</v>
       </c>
       <c r="M121" s="17">
+        <f t="shared" si="5"/>
+        <v>656.5</v>
+      </c>
+      <c r="N121" t="str">
         <f t="shared" si="3"/>
-        <v>656.5</v>
-      </c>
-      <c r="N121" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B121, $C$2:$C$649, C121, $D$2:$D$649, D121, $E$2:$E$649, E121) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -28571,11 +28569,11 @@
         <v>15075</v>
       </c>
       <c r="M122" s="17">
+        <f t="shared" si="5"/>
+        <v>645</v>
+      </c>
+      <c r="N122" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>645</v>
-      </c>
-      <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B122, $C$2:$C$649, C122, $D$2:$D$649, D122, $E$2:$E$649, E122) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O122" s="36" t="s">
@@ -28620,11 +28618,11 @@
         <v>9886</v>
       </c>
       <c r="M123" s="17">
+        <f t="shared" si="5"/>
+        <v>654</v>
+      </c>
+      <c r="N123" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>654</v>
-      </c>
-      <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B123, $C$2:$C$649, C123, $D$2:$D$649, D123, $E$2:$E$649, E123) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O123" s="36" t="s">
@@ -28669,11 +28667,11 @@
         <v>9470</v>
       </c>
       <c r="M124" s="17">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+      <c r="N124" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>300</v>
-      </c>
-      <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B124, $C$2:$C$649, C124, $D$2:$D$649, D124, $E$2:$E$649, E124) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -28715,11 +28713,11 @@
         <v>3180</v>
       </c>
       <c r="M125" s="17">
+        <f t="shared" si="5"/>
+        <v>300</v>
+      </c>
+      <c r="N125" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>300</v>
-      </c>
-      <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B125, $C$2:$C$649, C125, $D$2:$D$649, D125, $E$2:$E$649, E125) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -28755,7 +28753,7 @@
         <v>116</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B126, $C$2:$C$649, C126, $D$2:$D$649, D126, $E$2:$E$649, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28801,7 +28799,7 @@
         <v>500</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B127, $C$2:$C$649, C127, $D$2:$D$649, D127, $E$2:$E$649, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O127" s="37" t="s">
@@ -28850,7 +28848,7 @@
         <v>650</v>
       </c>
       <c r="N128" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B128, $C$2:$C$649, C128, $D$2:$D$649, D128, $E$2:$E$649, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="10"/>
@@ -28898,7 +28896,7 @@
         <v>300</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B129, $C$2:$C$649, C129, $D$2:$D$649, D129, $E$2:$E$649, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28944,7 +28942,7 @@
         <v>395</v>
       </c>
       <c r="N130" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B130, $C$2:$C$649, C130, $D$2:$D$649, D130, $E$2:$E$649, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="6">IF(COUNTIFS( $B$2:$B$649, B130, $C$2:$C$649, C130, $D$2:$D$649, D130, $E$2:$E$649, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O130" s="36" t="s">
@@ -28994,7 +28992,7 @@
         <v>250</v>
       </c>
       <c r="N131" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B131, $C$2:$C$649, C131, $D$2:$D$649, D131, $E$2:$E$649, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O131" s="36" t="s">
@@ -29034,7 +29032,7 @@
         <v>190</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B132, $C$2:$C$649, C132, $D$2:$D$649, D132, $E$2:$E$649, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29075,7 +29073,7 @@
       <c r="L133" s="17"/>
       <c r="M133" s="17"/>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B133, $C$2:$C$649, C133, $D$2:$D$649, D133, $E$2:$E$649, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="10"/>
@@ -29119,11 +29117,11 @@
         <v>39300</v>
       </c>
       <c r="M134" s="17">
-        <f t="shared" ref="M134:M139" si="4">ABS((D134*E134)-L134)</f>
+        <f t="shared" ref="M134:M139" si="7">ABS((D134*E134)-L134)</f>
         <v>18350</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B134, $C$2:$C$649, C134, $D$2:$D$649, D134, $E$2:$E$649, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29165,11 +29163,11 @@
         <v>10300</v>
       </c>
       <c r="M135" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B135, $C$2:$C$649, C135, $D$2:$D$649, D135, $E$2:$E$649, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P135" s="27"/>
@@ -29212,11 +29210,11 @@
         <v>8820</v>
       </c>
       <c r="M136" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>650</v>
       </c>
       <c r="N136" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B136, $C$2:$C$649, C136, $D$2:$D$649, D136, $E$2:$E$649, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="27"/>
@@ -29260,11 +29258,11 @@
         <v>36946</v>
       </c>
       <c r="M137" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>934</v>
       </c>
       <c r="N137" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B137, $C$2:$C$649, C137, $D$2:$D$649, D137, $E$2:$E$649, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="27"/>
@@ -29308,11 +29306,11 @@
         <v>10550</v>
       </c>
       <c r="M138" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>350</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B138, $C$2:$C$649, C138, $D$2:$D$649, D138, $E$2:$E$649, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29354,11 +29352,11 @@
         <v>5820</v>
       </c>
       <c r="M139" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B139, $C$2:$C$649, C139, $D$2:$D$649, D139, $E$2:$E$649, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29394,7 +29392,7 @@
         <v>116</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B140, $C$2:$C$649, C140, $D$2:$D$649, D140, $E$2:$E$649, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29440,7 +29438,7 @@
         <v>275</v>
       </c>
       <c r="N141" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B141, $C$2:$C$649, C141, $D$2:$D$649, D141, $E$2:$E$649, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -29486,7 +29484,7 @@
         <v>225</v>
       </c>
       <c r="N142" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B142, $C$2:$C$649, C142, $D$2:$D$649, D142, $E$2:$E$649, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -29522,7 +29520,7 @@
         <v>117</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B143, $C$2:$C$649, C143, $D$2:$D$649, D143, $E$2:$E$649, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29568,7 +29566,7 @@
         <v>650</v>
       </c>
       <c r="N144" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B144, $C$2:$C$649, C144, $D$2:$D$649, D144, $E$2:$E$649, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P144" s="27"/>
@@ -29603,7 +29601,7 @@
       </c>
       <c r="J145" s="32"/>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B145, $C$2:$C$649, C145, $D$2:$D$649, D145, $E$2:$E$649, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O145" s="27"/>
@@ -29650,7 +29648,7 @@
         <v>260</v>
       </c>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B146, $C$2:$C$649, C146, $D$2:$D$649, D146, $E$2:$E$649, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29696,7 +29694,7 @@
         <v>250</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B147, $C$2:$C$649, C147, $D$2:$D$649, D147, $E$2:$E$649, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29742,7 +29740,7 @@
         <v>504.5</v>
       </c>
       <c r="N148" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B148, $C$2:$C$649, C148, $D$2:$D$649, D148, $E$2:$E$649, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O148" s="36" t="s">
@@ -29792,7 +29790,7 @@
         <v>545</v>
       </c>
       <c r="N149" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B149, $C$2:$C$649, C149, $D$2:$D$649, D149, $E$2:$E$649, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O149" s="36" t="s">
@@ -29830,7 +29828,7 @@
       </c>
       <c r="J150" s="32"/>
       <c r="N150" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B150, $C$2:$C$649, C150, $D$2:$D$649, D150, $E$2:$E$649, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O150" s="36" t="s">
@@ -29870,7 +29868,7 @@
         <v>116</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B151, $C$2:$C$649, C151, $D$2:$D$649, D151, $E$2:$E$649, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29916,7 +29914,7 @@
         <v>300</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B152, $C$2:$C$649, C152, $D$2:$D$649, D152, $E$2:$E$649, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P152" s="10"/>
@@ -29963,7 +29961,7 @@
         <v>270</v>
       </c>
       <c r="N153" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B153, $C$2:$C$649, C153, $D$2:$D$649, D153, $E$2:$E$649, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="37" t="s">
@@ -30013,7 +30011,7 @@
         <v>188.60000000000014</v>
       </c>
       <c r="N154" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B154, $C$2:$C$649, C154, $D$2:$D$649, D154, $E$2:$E$649, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O154" s="37" t="s">
@@ -30063,7 +30061,7 @@
         <v>1700</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B155, $C$2:$C$649, C155, $D$2:$D$649, D155, $E$2:$E$649, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O155" s="27"/>
@@ -30110,7 +30108,7 @@
         <v>1000</v>
       </c>
       <c r="N156" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B156, $C$2:$C$649, C156, $D$2:$D$649, D156, $E$2:$E$649, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P156" s="27"/>
@@ -30147,7 +30145,7 @@
         <v>117</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B157, $C$2:$C$649, C157, $D$2:$D$649, D157, $E$2:$E$649, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30193,7 +30191,7 @@
         <v>34175</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B158, $C$2:$C$649, C158, $D$2:$D$649, D158, $E$2:$E$649, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30239,7 +30237,7 @@
         <v>646</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B159, $C$2:$C$649, C159, $D$2:$D$649, D159, $E$2:$E$649, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="36" t="s">
@@ -30281,7 +30279,7 @@
       <c r="L160" s="16"/>
       <c r="M160" s="16"/>
       <c r="N160" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B160, $C$2:$C$649, C160, $D$2:$D$649, D160, $E$2:$E$649, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O160"/>
@@ -30317,7 +30315,7 @@
       </c>
       <c r="J161" s="32"/>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B161, $C$2:$C$649, C161, $D$2:$D$649, D161, $E$2:$E$649, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30363,7 +30361,7 @@
         <v>300</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B162, $C$2:$C$649, C162, $D$2:$D$649, D162, $E$2:$E$649, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30397,7 +30395,7 @@
       </c>
       <c r="J163" s="32"/>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B163, $C$2:$C$649, C163, $D$2:$D$649, D163, $E$2:$E$649, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30443,7 +30441,7 @@
         <v>300</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B164, $C$2:$C$649, C164, $D$2:$D$649, D164, $E$2:$E$649, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O164" s="36" t="s">
@@ -30492,7 +30490,7 @@
         <v>450</v>
       </c>
       <c r="N165" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B165, $C$2:$C$649, C165, $D$2:$D$649, D165, $E$2:$E$649, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P165"/>
@@ -30539,7 +30537,7 @@
         <v>300</v>
       </c>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B166, $C$2:$C$649, C166, $D$2:$D$649, D166, $E$2:$E$649, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30575,7 +30573,7 @@
         <v>116</v>
       </c>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B167, $C$2:$C$649, C167, $D$2:$D$649, D167, $E$2:$E$649, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30611,7 +30609,7 @@
         <v>117</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B168, $C$2:$C$649, C168, $D$2:$D$649, D168, $E$2:$E$649, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30657,7 +30655,7 @@
         <v>800</v>
       </c>
       <c r="N169" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B169, $C$2:$C$649, C169, $D$2:$D$649, D169, $E$2:$E$649, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30693,7 +30691,7 @@
         <v>117</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B170, $C$2:$C$649, C170, $D$2:$D$649, D170, $E$2:$E$649, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O170" s="36" t="s">
@@ -30742,7 +30740,7 @@
         <v>300</v>
       </c>
       <c r="N171" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B171, $C$2:$C$649, C171, $D$2:$D$649, D171, $E$2:$E$649, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O171"/>
@@ -30778,7 +30776,7 @@
       </c>
       <c r="J172" s="32"/>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B172, $C$2:$C$649, C172, $D$2:$D$649, D172, $E$2:$E$649, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P172" s="27"/>
@@ -30813,7 +30811,7 @@
       </c>
       <c r="J173" s="32"/>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B173, $C$2:$C$649, C173, $D$2:$D$649, D173, $E$2:$E$649, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30859,7 +30857,7 @@
         <v>275</v>
       </c>
       <c r="N174" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B174, $C$2:$C$649, C174, $D$2:$D$649, D174, $E$2:$E$649, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30905,7 +30903,7 @@
         <v>940</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B175, $C$2:$C$649, C175, $D$2:$D$649, D175, $E$2:$E$649, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30939,7 +30937,7 @@
       </c>
       <c r="J176" s="32"/>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B176, $C$2:$C$649, C176, $D$2:$D$649, D176, $E$2:$E$649, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30985,7 +30983,7 @@
         <v>290</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B177, $C$2:$C$649, C177, $D$2:$D$649, D177, $E$2:$E$649, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31019,7 +31017,7 @@
       </c>
       <c r="J178" s="32"/>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B178, $C$2:$C$649, C178, $D$2:$D$649, D178, $E$2:$E$649, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31055,7 +31053,7 @@
         <v>117</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B179, $C$2:$C$649, C179, $D$2:$D$649, D179, $E$2:$E$649, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31091,7 +31089,7 @@
         <v>116</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B180, $C$2:$C$649, C180, $D$2:$D$649, D180, $E$2:$E$649, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31137,7 +31135,7 @@
         <v>650</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B181, $C$2:$C$649, C181, $D$2:$D$649, D181, $E$2:$E$649, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O181" s="27"/>
@@ -31184,7 +31182,7 @@
         <v>300</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B182, $C$2:$C$649, C182, $D$2:$D$649, D182, $E$2:$E$649, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31230,7 +31228,7 @@
         <v>300</v>
       </c>
       <c r="N183" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B183, $C$2:$C$649, C183, $D$2:$D$649, D183, $E$2:$E$649, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31264,7 +31262,7 @@
       </c>
       <c r="J184" s="32"/>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B184, $C$2:$C$649, C184, $D$2:$D$649, D184, $E$2:$E$649, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31310,7 +31308,7 @@
         <v>300</v>
       </c>
       <c r="N185" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B185, $C$2:$C$649, C185, $D$2:$D$649, D185, $E$2:$E$649, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="36" t="s">
@@ -31359,7 +31357,7 @@
         <v>253</v>
       </c>
       <c r="N186" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B186, $C$2:$C$649, C186, $D$2:$D$649, D186, $E$2:$E$649, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O186" s="36" t="s">
@@ -31408,7 +31406,7 @@
         <v>355.5</v>
       </c>
       <c r="N187" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B187, $C$2:$C$649, C187, $D$2:$D$649, D187, $E$2:$E$649, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O187" s="36" t="s">
@@ -31448,7 +31446,7 @@
         <v>117</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B188, $C$2:$C$649, C188, $D$2:$D$649, D188, $E$2:$E$649, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31494,7 +31492,7 @@
         <v>150</v>
       </c>
       <c r="N189" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B189, $C$2:$C$649, C189, $D$2:$D$649, D189, $E$2:$E$649, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -31540,7 +31538,7 @@
         <v>250</v>
       </c>
       <c r="N190" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B190, $C$2:$C$649, C190, $D$2:$D$649, D190, $E$2:$E$649, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -31574,7 +31572,7 @@
       </c>
       <c r="J191" s="32"/>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B191, $C$2:$C$649, C191, $D$2:$D$649, D191, $E$2:$E$649, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P191" s="27"/>
@@ -31609,7 +31607,7 @@
       </c>
       <c r="J192" s="32"/>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B192, $C$2:$C$649, C192, $D$2:$D$649, D192, $E$2:$E$649, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="22"/>
@@ -31646,7 +31644,7 @@
         <v>54</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B193, $C$2:$C$649, C193, $D$2:$D$649, D193, $E$2:$E$649, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31692,7 +31690,7 @@
         <v>501</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B194, $C$2:$C$649, C194, $D$2:$D$649, D194, $E$2:$E$649, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="8">IF(COUNTIFS( $B$2:$B$649, B194, $C$2:$C$649, C194, $D$2:$D$649, D194, $E$2:$E$649, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O194" s="36" t="s">
@@ -31741,7 +31739,7 @@
         <v>360</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B195, $C$2:$C$649, C195, $D$2:$D$649, D195, $E$2:$E$649, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31775,7 +31773,7 @@
       </c>
       <c r="J196" s="32"/>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B196, $C$2:$C$649, C196, $D$2:$D$649, D196, $E$2:$E$649, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31821,7 +31819,7 @@
         <v>250</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B197, $C$2:$C$649, C197, $D$2:$D$649, D197, $E$2:$E$649, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31867,7 +31865,7 @@
         <v>300</v>
       </c>
       <c r="N198" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B198, $C$2:$C$649, C198, $D$2:$D$649, D198, $E$2:$E$649, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O198" s="10"/>
@@ -31915,7 +31913,7 @@
         <v>376</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B199, $C$2:$C$649, C199, $D$2:$D$649, D199, $E$2:$E$649, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="10"/>
@@ -31953,7 +31951,7 @@
         <v>117</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B200, $C$2:$C$649, C200, $D$2:$D$649, D200, $E$2:$E$649, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O200" s="27"/>
@@ -31993,7 +31991,7 @@
       <c r="L201" s="16"/>
       <c r="M201" s="16"/>
       <c r="N201" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B201, $C$2:$C$649, C201, $D$2:$D$649, D201, $E$2:$E$649, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32039,7 +32037,7 @@
         <v>527.5</v>
       </c>
       <c r="N202" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B202, $C$2:$C$649, C202, $D$2:$D$649, D202, $E$2:$E$649, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O202" s="27"/>
@@ -32082,7 +32080,7 @@
       <c r="L203" s="25"/>
       <c r="M203" s="25"/>
       <c r="N203" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B203, $C$2:$C$649, C203, $D$2:$D$649, D203, $E$2:$E$649, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O203" s="27"/>
@@ -32120,7 +32118,7 @@
         <v>116</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B204, $C$2:$C$649, C204, $D$2:$D$649, D204, $E$2:$E$649, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P204" s="27"/>
@@ -32167,7 +32165,7 @@
         <v>260</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B205, $C$2:$C$649, C205, $D$2:$D$649, D205, $E$2:$E$649, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32213,7 +32211,7 @@
         <v>300</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B206, $C$2:$C$649, C206, $D$2:$D$649, D206, $E$2:$E$649, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32259,7 +32257,7 @@
         <v>268</v>
       </c>
       <c r="N207" s="58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B207, $C$2:$C$649, C207, $D$2:$D$649, D207, $E$2:$E$649, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="22"/>
@@ -32309,7 +32307,7 @@
         <v>650</v>
       </c>
       <c r="N208" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B208, $C$2:$C$649, C208, $D$2:$D$649, D208, $E$2:$E$649, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P208" s="27"/>
@@ -32347,7 +32345,7 @@
       <c r="L209" s="17"/>
       <c r="M209" s="17"/>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B209, $C$2:$C$649, C209, $D$2:$D$649, D209, $E$2:$E$649, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O209" s="10"/>
@@ -32383,7 +32381,7 @@
       </c>
       <c r="J210" s="32"/>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B210, $C$2:$C$649, C210, $D$2:$D$649, D210, $E$2:$E$649, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32419,7 +32417,7 @@
         <v>117</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B211, $C$2:$C$649, C211, $D$2:$D$649, D211, $E$2:$E$649, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O211" s="27"/>
@@ -32466,7 +32464,7 @@
         <v>500</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B212, $C$2:$C$649, C212, $D$2:$D$649, D212, $E$2:$E$649, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32512,7 +32510,7 @@
         <v>300</v>
       </c>
       <c r="N213" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B213, $C$2:$C$649, C213, $D$2:$D$649, D213, $E$2:$E$649, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32558,7 +32556,7 @@
         <v>188</v>
       </c>
       <c r="N214" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B214, $C$2:$C$649, C214, $D$2:$D$649, D214, $E$2:$E$649, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="27"/>
@@ -32599,7 +32597,7 @@
       <c r="L215" s="16"/>
       <c r="M215" s="16"/>
       <c r="N215" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B215, $C$2:$C$649, C215, $D$2:$D$649, D215, $E$2:$E$649, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P215" s="22"/>
@@ -32646,7 +32644,7 @@
         <v>400</v>
       </c>
       <c r="N216" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B216, $C$2:$C$649, C216, $D$2:$D$649, D216, $E$2:$E$649, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32692,7 +32690,7 @@
         <v>500</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B217, $C$2:$C$649, C217, $D$2:$D$649, D217, $E$2:$E$649, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32738,7 +32736,7 @@
         <v>300</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B218, $C$2:$C$649, C218, $D$2:$D$649, D218, $E$2:$E$649, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O218" s="36" t="s">
@@ -32780,7 +32778,7 @@
       <c r="L219" s="17"/>
       <c r="M219" s="17"/>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B219, $C$2:$C$649, C219, $D$2:$D$649, D219, $E$2:$E$649, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P219" s="10"/>
@@ -32827,7 +32825,7 @@
         <v>816</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B220, $C$2:$C$649, C220, $D$2:$D$649, D220, $E$2:$E$649, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32873,7 +32871,7 @@
         <v>300</v>
       </c>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B221, $C$2:$C$649, C221, $D$2:$D$649, D221, $E$2:$E$649, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="10"/>
@@ -32911,7 +32909,7 @@
         <v>116</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B222, $C$2:$C$649, C222, $D$2:$D$649, D222, $E$2:$E$649, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32950,7 +32948,7 @@
       <c r="L223" s="17"/>
       <c r="M223" s="17"/>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B223, $C$2:$C$649, C223, $D$2:$D$649, D223, $E$2:$E$649, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O223" s="10"/>
@@ -32998,7 +32996,7 @@
         <v>250</v>
       </c>
       <c r="N224" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B224, $C$2:$C$649, C224, $D$2:$D$649, D224, $E$2:$E$649, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O224" s="10"/>
@@ -33036,7 +33034,7 @@
         <v>117</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B225, $C$2:$C$649, C225, $D$2:$D$649, D225, $E$2:$E$649, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33078,11 +33076,11 @@
         <v>3521</v>
       </c>
       <c r="M226" s="17">
-        <f t="shared" ref="M226:M231" si="5">ABS((D226*E226)-L226)</f>
+        <f t="shared" ref="M226:M231" si="9">ABS((D226*E226)-L226)</f>
         <v>250</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B226, $C$2:$C$649, C226, $D$2:$D$649, D226, $E$2:$E$649, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33124,11 +33122,11 @@
         <v>8480</v>
       </c>
       <c r="M227" s="24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>280</v>
       </c>
       <c r="N227" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B227, $C$2:$C$649, C227, $D$2:$D$649, D227, $E$2:$E$649, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33170,11 +33168,11 @@
         <v>4264</v>
       </c>
       <c r="M228" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>320</v>
       </c>
       <c r="N228" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B228, $C$2:$C$649, C228, $D$2:$D$649, D228, $E$2:$E$649, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33216,11 +33214,11 @@
         <v>5282</v>
       </c>
       <c r="M229" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>448</v>
       </c>
       <c r="N229" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B229, $C$2:$C$649, C229, $D$2:$D$649, D229, $E$2:$E$649, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33262,11 +33260,11 @@
         <v>14400</v>
       </c>
       <c r="M230" s="17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>500</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B230, $C$2:$C$649, C230, $D$2:$D$649, D230, $E$2:$E$649, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33308,11 +33306,11 @@
         <v>13030</v>
       </c>
       <c r="M231" s="17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>370</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B231, $C$2:$C$649, C231, $D$2:$D$649, D231, $E$2:$E$649, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P231" s="27"/>
@@ -33349,7 +33347,7 @@
         <v>54</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B232, $C$2:$C$649, C232, $D$2:$D$649, D232, $E$2:$E$649, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33383,7 +33381,7 @@
       </c>
       <c r="J233" s="32"/>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B233, $C$2:$C$649, C233, $D$2:$D$649, D233, $E$2:$E$649, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33429,7 +33427,7 @@
         <v>290</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B234, $C$2:$C$649, C234, $D$2:$D$649, D234, $E$2:$E$649, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33463,7 +33461,7 @@
       </c>
       <c r="J235" s="32"/>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B235, $C$2:$C$649, C235, $D$2:$D$649, D235, $E$2:$E$649, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33509,7 +33507,7 @@
         <v>800</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B236, $C$2:$C$649, C236, $D$2:$D$649, D236, $E$2:$E$649, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O236" s="36" t="s">
@@ -33546,7 +33544,7 @@
       </c>
       <c r="J237" s="32"/>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B237, $C$2:$C$649, C237, $D$2:$D$649, D237, $E$2:$E$649, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33592,7 +33590,7 @@
         <v>450</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B238, $C$2:$C$649, C238, $D$2:$D$649, D238, $E$2:$E$649, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33638,7 +33636,7 @@
         <v>300</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B239, $C$2:$C$649, C239, $D$2:$D$649, D239, $E$2:$E$649, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O239" s="10"/>
@@ -33686,7 +33684,7 @@
         <v>48320</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B240, $C$2:$C$649, C240, $D$2:$D$649, D240, $E$2:$E$649, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O240" s="36" t="s">
@@ -33736,7 +33734,7 @@
         <v>1000</v>
       </c>
       <c r="N241" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B241, $C$2:$C$649, C241, $D$2:$D$649, D241, $E$2:$E$649, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33775,7 +33773,7 @@
         <v>144</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B242, $C$2:$C$649, C242, $D$2:$D$649, D242, $E$2:$E$649, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33809,7 +33807,7 @@
       </c>
       <c r="J243" s="32"/>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B243, $C$2:$C$649, C243, $D$2:$D$649, D243, $E$2:$E$649, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33845,7 +33843,7 @@
         <v>116</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B244, $C$2:$C$649, C244, $D$2:$D$649, D244, $E$2:$E$649, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33879,7 +33877,7 @@
       </c>
       <c r="J245" s="32"/>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B245, $C$2:$C$649, C245, $D$2:$D$649, D245, $E$2:$E$649, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33913,7 +33911,7 @@
       </c>
       <c r="J246" s="32"/>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B246, $C$2:$C$649, C246, $D$2:$D$649, D246, $E$2:$E$649, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33959,7 +33957,7 @@
         <v>140</v>
       </c>
       <c r="N247" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B247, $C$2:$C$649, C247, $D$2:$D$649, D247, $E$2:$E$649, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
       <c r="P247" s="27"/>
@@ -34006,7 +34004,7 @@
         <v>300</v>
       </c>
       <c r="N248" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B248, $C$2:$C$649, C248, $D$2:$D$649, D248, $E$2:$E$649, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -34042,7 +34040,7 @@
         <v>117</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B249, $C$2:$C$649, C249, $D$2:$D$649, D249, $E$2:$E$649, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34088,7 +34086,7 @@
         <v>500</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B250, $C$2:$C$649, C250, $D$2:$D$649, D250, $E$2:$E$649, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34134,7 +34132,7 @@
         <v>420</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B251, $C$2:$C$649, C251, $D$2:$D$649, D251, $E$2:$E$649, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34170,7 +34168,7 @@
         <v>117</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B252, $C$2:$C$649, C252, $D$2:$D$649, D252, $E$2:$E$649, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34209,7 +34207,7 @@
       <c r="L253" s="16"/>
       <c r="M253" s="16"/>
       <c r="N253" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B253, $C$2:$C$649, C253, $D$2:$D$649, D253, $E$2:$E$649, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O253"/>
@@ -34256,7 +34254,7 @@
         <v>250</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B254, $C$2:$C$649, C254, $D$2:$D$649, D254, $E$2:$E$649, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P254" s="27"/>
@@ -34303,7 +34301,7 @@
         <v>300</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B255, $C$2:$C$649, C255, $D$2:$D$649, D255, $E$2:$E$649, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34337,7 +34335,7 @@
       </c>
       <c r="J256" s="32"/>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B256, $C$2:$C$649, C256, $D$2:$D$649, D256, $E$2:$E$649, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="27"/>
@@ -34384,7 +34382,7 @@
         <v>47900</v>
       </c>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B257, $C$2:$C$649, C257, $D$2:$D$649, D257, $E$2:$E$649, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O257" s="36" t="s">
@@ -34433,7 +34431,7 @@
         <v>650</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B258, $C$2:$C$649, C258, $D$2:$D$649, D258, $E$2:$E$649, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N316" si="10">IF(COUNTIFS( $B$2:$B$649, B258, $C$2:$C$649, C258, $D$2:$D$649, D258, $E$2:$E$649, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O258" s="36" t="s">
@@ -34482,7 +34480,7 @@
         <v>495</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B259, $C$2:$C$649, C259, $D$2:$D$649, D259, $E$2:$E$649, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O259" s="36" t="s">
@@ -34521,7 +34519,7 @@
         <v>117</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B260, $C$2:$C$649, C260, $D$2:$D$649, D260, $E$2:$E$649, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34555,7 +34553,7 @@
       </c>
       <c r="J261" s="32"/>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B261, $C$2:$C$649, C261, $D$2:$D$649, D261, $E$2:$E$649, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P261" s="27"/>
@@ -34602,7 +34600,7 @@
         <v>300</v>
       </c>
       <c r="N262" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B262, $C$2:$C$649, C262, $D$2:$D$649, D262, $E$2:$E$649, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O262" s="10"/>
@@ -34650,7 +34648,7 @@
         <v>450</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B263, $C$2:$C$649, C263, $D$2:$D$649, D263, $E$2:$E$649, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34689,7 +34687,7 @@
       <c r="L264" s="17"/>
       <c r="M264" s="17"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B264, $C$2:$C$649, C264, $D$2:$D$649, D264, $E$2:$E$649, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O264" s="10"/>
@@ -34737,7 +34735,7 @@
         <v>300</v>
       </c>
       <c r="N265" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B265, $C$2:$C$649, C265, $D$2:$D$649, D265, $E$2:$E$649, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="36" t="s">
@@ -34775,7 +34773,7 @@
       </c>
       <c r="J266" s="32"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B266, $C$2:$C$649, C266, $D$2:$D$649, D266, $E$2:$E$649, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O266" s="27"/>
@@ -34812,7 +34810,7 @@
         <v>116</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B267, $C$2:$C$649, C267, $D$2:$D$649, D267, $E$2:$E$649, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34848,7 +34846,7 @@
         <v>116</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B268, $C$2:$C$649, C268, $D$2:$D$649, D268, $E$2:$E$649, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34894,7 +34892,7 @@
         <v>650</v>
       </c>
       <c r="N269" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B269, $C$2:$C$649, C269, $D$2:$D$649, D269, $E$2:$E$649, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O269"/>
@@ -34932,7 +34930,7 @@
         <v>116</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B270, $C$2:$C$649, C270, $D$2:$D$649, D270, $E$2:$E$649, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34978,7 +34976,7 @@
         <v>47480</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B271, $C$2:$C$649, C271, $D$2:$D$649, D271, $E$2:$E$649, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35024,7 +35022,7 @@
         <v>1800</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B272, $C$2:$C$649, C272, $D$2:$D$649, D272, $E$2:$E$649, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35070,7 +35068,7 @@
         <v>340</v>
       </c>
       <c r="N273" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B273, $C$2:$C$649, C273, $D$2:$D$649, D273, $E$2:$E$649, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35106,7 +35104,7 @@
         <v>116</v>
       </c>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B274, $C$2:$C$649, C274, $D$2:$D$649, D274, $E$2:$E$649, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35142,7 +35140,7 @@
         <v>116</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B275, $C$2:$C$649, C275, $D$2:$D$649, D275, $E$2:$E$649, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35188,7 +35186,7 @@
         <v>300</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B276, $C$2:$C$649, C276, $D$2:$D$649, D276, $E$2:$E$649, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35234,7 +35232,7 @@
         <v>250</v>
       </c>
       <c r="N277" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B277, $C$2:$C$649, C277, $D$2:$D$649, D277, $E$2:$E$649, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35280,7 +35278,7 @@
         <v>300</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B278, $C$2:$C$649, C278, $D$2:$D$649, D278, $E$2:$E$649, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35316,7 +35314,7 @@
         <v>116</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B279, $C$2:$C$649, C279, $D$2:$D$649, D279, $E$2:$E$649, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35357,7 +35355,7 @@
       <c r="L280" s="16"/>
       <c r="M280" s="16"/>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B280, $C$2:$C$649, C280, $D$2:$D$649, D280, $E$2:$E$649, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35391,7 +35389,7 @@
       </c>
       <c r="J281" s="32"/>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B281, $C$2:$C$649, C281, $D$2:$D$649, D281, $E$2:$E$649, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35427,7 +35425,7 @@
         <v>117</v>
       </c>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B282, $C$2:$C$649, C282, $D$2:$D$649, D282, $E$2:$E$649, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35473,7 +35471,7 @@
         <v>480</v>
       </c>
       <c r="N283" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B283, $C$2:$C$649, C283, $D$2:$D$649, D283, $E$2:$E$649, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35507,7 +35505,7 @@
       </c>
       <c r="J284" s="32"/>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B284, $C$2:$C$649, C284, $D$2:$D$649, D284, $E$2:$E$649, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35543,7 +35541,7 @@
         <v>152</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B285, $C$2:$C$649, C285, $D$2:$D$649, D285, $E$2:$E$649, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35577,7 +35575,7 @@
       </c>
       <c r="J286" s="32"/>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B286, $C$2:$C$649, C286, $D$2:$D$649, D286, $E$2:$E$649, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35623,7 +35621,7 @@
         <v>285</v>
       </c>
       <c r="N287" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B287, $C$2:$C$649, C287, $D$2:$D$649, D287, $E$2:$E$649, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35669,7 +35667,7 @@
         <v>726</v>
       </c>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B288, $C$2:$C$649, C288, $D$2:$D$649, D288, $E$2:$E$649, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35705,7 +35703,7 @@
         <v>116</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B289, $C$2:$C$649, C289, $D$2:$D$649, D289, $E$2:$E$649, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35739,7 +35737,7 @@
       </c>
       <c r="J290" s="32"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B290, $C$2:$C$649, C290, $D$2:$D$649, D290, $E$2:$E$649, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35773,7 +35771,7 @@
       </c>
       <c r="J291" s="32"/>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B291, $C$2:$C$649, C291, $D$2:$D$649, D291, $E$2:$E$649, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35819,7 +35817,7 @@
         <v>275</v>
       </c>
       <c r="N292" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B292, $C$2:$C$649, C292, $D$2:$D$649, D292, $E$2:$E$649, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35855,7 +35853,7 @@
         <v>54</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B293, $C$2:$C$649, C293, $D$2:$D$649, D293, $E$2:$E$649, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35901,7 +35899,7 @@
         <v>250</v>
       </c>
       <c r="N294" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B294, $C$2:$C$649, C294, $D$2:$D$649, D294, $E$2:$E$649, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P294" s="27"/>
@@ -35948,7 +35946,7 @@
         <v>300</v>
       </c>
       <c r="N295" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B295, $C$2:$C$649, C295, $D$2:$D$649, D295, $E$2:$E$649, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35994,7 +35992,7 @@
         <v>235</v>
       </c>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B296, $C$2:$C$649, C296, $D$2:$D$649, D296, $E$2:$E$649, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36028,7 +36026,7 @@
       </c>
       <c r="J297" s="32"/>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B297, $C$2:$C$649, C297, $D$2:$D$649, D297, $E$2:$E$649, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36062,7 +36060,7 @@
       </c>
       <c r="J298" s="32"/>
       <c r="N298" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B298, $C$2:$C$649, C298, $D$2:$D$649, D298, $E$2:$E$649, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36098,7 +36096,7 @@
         <v>117</v>
       </c>
       <c r="N299" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B299, $C$2:$C$649, C299, $D$2:$D$649, D299, $E$2:$E$649, E299) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36132,7 +36130,7 @@
       </c>
       <c r="J300" s="32"/>
       <c r="N300" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B300, $C$2:$C$649, C300, $D$2:$D$649, D300, $E$2:$E$649, E300) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36168,7 +36166,7 @@
         <v>117</v>
       </c>
       <c r="N301" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B301, $C$2:$C$649, C301, $D$2:$D$649, D301, $E$2:$E$649, E301) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36204,7 +36202,7 @@
         <v>117</v>
       </c>
       <c r="N302" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B302, $C$2:$C$649, C302, $D$2:$D$649, D302, $E$2:$E$649, E302) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36250,7 +36248,7 @@
         <v>250</v>
       </c>
       <c r="N303" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B303, $C$2:$C$649, C303, $D$2:$D$649, D303, $E$2:$E$649, E303) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36289,7 +36287,7 @@
       <c r="L304" s="25"/>
       <c r="M304" s="25"/>
       <c r="N304" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B304, $C$2:$C$649, C304, $D$2:$D$649, D304, $E$2:$E$649, E304) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O304" s="27"/>
@@ -36330,7 +36328,7 @@
       <c r="L305" s="25"/>
       <c r="M305" s="25"/>
       <c r="N305" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B305, $C$2:$C$649, C305, $D$2:$D$649, D305, $E$2:$E$649, E305) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O305" s="27"/>
@@ -36368,7 +36366,7 @@
         <v>116</v>
       </c>
       <c r="N306" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B306, $C$2:$C$649, C306, $D$2:$D$649, D306, $E$2:$E$649, E306) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36406,7 +36404,7 @@
         <v>271.80000000000018</v>
       </c>
       <c r="N307" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B307, $C$2:$C$649, C307, $D$2:$D$649, D307, $E$2:$E$649, E307) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36440,11 +36438,11 @@
         <v>17960</v>
       </c>
       <c r="M308" s="17">
-        <f t="shared" ref="M308:M316" si="6">ABS((D308*E308)-L308)</f>
+        <f t="shared" ref="M308:M316" si="11">ABS((D308*E308)-L308)</f>
         <v>650</v>
       </c>
       <c r="N308" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B308, $C$2:$C$649, C308, $D$2:$D$649, D308, $E$2:$E$649, E308) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36478,11 +36476,11 @@
         <v>41650</v>
       </c>
       <c r="M309" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>700</v>
       </c>
       <c r="N309" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B309, $C$2:$C$649, C309, $D$2:$D$649, D309, $E$2:$E$649, E309) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36517,11 +36515,11 @@
         <v>3865</v>
       </c>
       <c r="M310" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>135</v>
       </c>
       <c r="N310" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B310, $C$2:$C$649, C310, $D$2:$D$649, D310, $E$2:$E$649, E310) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36556,11 +36554,11 @@
         <v>3865</v>
       </c>
       <c r="M311" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>235</v>
       </c>
       <c r="N311" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B311, $C$2:$C$649, C311, $D$2:$D$649, D311, $E$2:$E$649, E311) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36594,11 +36592,11 @@
         <v>3550</v>
       </c>
       <c r="M312" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>250</v>
       </c>
       <c r="N312" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B312, $C$2:$C$649, C312, $D$2:$D$649, D312, $E$2:$E$649, E312) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36633,11 +36631,11 @@
         <v>5660</v>
       </c>
       <c r="M313" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>240</v>
       </c>
       <c r="N313" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B313, $C$2:$C$649, C313, $D$2:$D$649, D313, $E$2:$E$649, E313) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36671,11 +36669,11 @@
         <v>3810</v>
       </c>
       <c r="M314" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>250</v>
       </c>
       <c r="N314" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B314, $C$2:$C$649, C314, $D$2:$D$649, D314, $E$2:$E$649, E314) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36709,11 +36707,11 @@
         <v>3450</v>
       </c>
       <c r="M315" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>250</v>
       </c>
       <c r="N315" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B315, $C$2:$C$649, C315, $D$2:$D$649, D315, $E$2:$E$649, E315) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -36748,11 +36746,11 @@
         <v>2830</v>
       </c>
       <c r="M316" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>220</v>
       </c>
       <c r="N316" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$649, B316, $C$2:$C$649, C316, $D$2:$D$649, D316, $E$2:$E$649, E316) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
